--- a/Src/Assets/StreamingAssets/Common/Tables/Tables/Skill&Buff.xlsx
+++ b/Src/Assets/StreamingAssets/Common/Tables/Tables/Skill&Buff.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CCA\Src\Assets\Common\Tables\Tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CCA\Src\Assets\StreamingAssets\Common\Tables\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61DBB84D-551E-495C-A1B5-59B48C8D82A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8540D561-90AD-49DE-A00B-1D3C15379C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TableExplanation" sheetId="5" r:id="rId1"/>
@@ -1513,30 +1513,9 @@
     <t>丝线编织成茧，我将重新归来</t>
   </si>
   <si>
-    <t>你每受到或进行一次攻击，你获得1点“记忆灵丝”。当你生命值≤0时，若“记忆灵丝”数量＞4，你进入“结茧”状态，重生时恢复初始状态。此技能仅生效一次</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>化茧</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cocooning</t>
-  </si>
-  <si>
     <t>时钟拨回起点，让我们重新演绎这场闹剧</t>
   </si>
   <si>
-    <t>当你生命值为≤0时，若场上有虚空兽存在，一只虚空兽立刻变为“茧”，你借此茧重生</t>
-  </si>
-  <si>
-    <t>时序逆转</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Time Reversal</t>
-  </si>
-  <si>
     <t>（低吼声……）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1574,13 +1553,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>扭曲时空，令时间之手对玩家追击一次“砍”，记忆之手对玩家追击一次“给枪”。若二者资源不足以发动，消耗所有资源，依然发动。</t>
-  </si>
-  <si>
-    <t>吞噬星空</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Devour the Stars</t>
   </si>
   <si>
@@ -1604,17 +1576,6 @@
   <si>
     <t>我的，不可置疑</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>下一回合，你使用“补给”类行动时，额外获得3点刀剑与2点子弹。下一回合，你使用非“补给”类行动时，刷新该技能CD。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>威压</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Intimidation</t>
   </si>
   <si>
     <t>力不竭、战不止</t>
@@ -1810,9 +1771,6 @@
   </si>
   <si>
     <t>Bloodborne Rebirth</t>
-  </si>
-  <si>
-    <t>当你防御或反制成功时，你下回合攻击力+1</t>
   </si>
   <si>
     <t>突跃反击</t>
@@ -1950,9 +1908,6 @@
   </si>
   <si>
     <t>Blazing Dance</t>
-  </si>
-  <si>
-    <t>接下来的3个回合内，你可以在追击阶段仅一次使用一张免费的“刺”，追击后进入CD</t>
   </si>
   <si>
     <t>短匕</t>
@@ -2201,6 +2156,58 @@
     <t>下回合你的所有伤害+1，攻击力+0.5</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>回合开始时发动，若有足够的资源，令时间之手对玩家追击一次“砍”，或记忆之手对玩家追击一次“给枪”。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>吞噬星空（修改）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Time Reversal</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>倒转时空</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>当你生命值为≤0时，若场上有虚空兽存在，一只虚空兽立刻变为“茧”，你借此茧重生</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Time Fasting</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间加速</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有友方下一回合的行动将会额外执行一次</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Time Distortion</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>时空扭曲</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>下一回合，所有人将额外执行一次这轮的行动。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>你可以在追击阶段仅一次使用一张免费的“刺”，追击后进入CD</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>当你防御或反制成功时，你下回合攻击力+1.5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -2218,6 +2225,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2781,7 +2789,7 @@
     </row>
     <row r="3" spans="1:18" ht="25" x14ac:dyDescent="0.5">
       <c r="A3" s="32" t="s">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="Q3" s="31"/>
       <c r="R3" s="31"/>
@@ -2792,56 +2800,56 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="30" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="Q5" s="31"/>
       <c r="R5" s="31"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="30" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
       <c r="Q6" s="31"/>
       <c r="R6" s="31"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="30" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="Q7" s="31"/>
       <c r="R7" s="31"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="30" t="s">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="Q8" s="31"/>
       <c r="R8" s="31"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="30" t="s">
-        <v>512</v>
+        <v>499</v>
       </c>
       <c r="Q9" s="31"/>
       <c r="R9" s="31"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="30" t="s">
-        <v>511</v>
+        <v>498</v>
       </c>
       <c r="Q10" s="31"/>
       <c r="R10" s="31"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="30" t="s">
-        <v>510</v>
+        <v>497</v>
       </c>
       <c r="Q11" s="31"/>
       <c r="R11" s="31"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="30" t="s">
-        <v>509</v>
+        <v>496</v>
       </c>
       <c r="Q12" s="31"/>
       <c r="R12" s="31"/>
@@ -3232,19 +3240,19 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="28" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>508</v>
+        <v>495</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="E1" s="29" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="F1" s="28"/>
       <c r="G1" s="28"/>
@@ -3260,17 +3268,17 @@
         <v>1</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>506</v>
+        <v>493</v>
       </c>
       <c r="C2" s="23" t="str">
         <f t="shared" ref="C2:C10" si="0">B2</f>
         <v>Diving</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>505</v>
+        <v>492</v>
       </c>
       <c r="E2" s="24" t="s">
-        <v>504</v>
+        <v>491</v>
       </c>
       <c r="F2" s="23"/>
       <c r="G2" s="23"/>
@@ -3286,17 +3294,17 @@
         <v>2</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>503</v>
+        <v>490</v>
       </c>
       <c r="C3" s="21" t="str">
         <f t="shared" si="0"/>
         <v>Stunned</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>501</v>
+        <v>488</v>
       </c>
       <c r="R3" s="27"/>
       <c r="S3" s="27"/>
@@ -3306,17 +3314,17 @@
         <v>3</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>500</v>
+        <v>487</v>
       </c>
       <c r="C4" s="23" t="str">
         <f t="shared" si="0"/>
         <v>Invincible</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>499</v>
+        <v>486</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="F4" s="23"/>
       <c r="G4" s="23"/>
@@ -3334,17 +3342,17 @@
         <v>4</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="C5" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Critical</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>496</v>
+        <v>483</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>495</v>
+        <v>482</v>
       </c>
       <c r="F5" s="25"/>
       <c r="G5" s="25"/>
@@ -3362,17 +3370,17 @@
         <v>5</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>494</v>
+        <v>481</v>
       </c>
       <c r="C6" s="23" t="str">
         <f t="shared" si="0"/>
         <v>Slowed</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>492</v>
+        <v>479</v>
       </c>
       <c r="F6" s="23"/>
       <c r="G6" s="23"/>
@@ -3390,17 +3398,17 @@
         <v>6</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="C7" s="21" t="str">
         <f t="shared" si="0"/>
         <v>Burning</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="R7" s="27"/>
       <c r="S7" s="27"/>
@@ -3410,17 +3418,17 @@
         <v>7</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="C8" s="23" t="str">
         <f t="shared" si="0"/>
         <v>Cocooned</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>486</v>
+        <v>473</v>
       </c>
       <c r="F8" s="23"/>
       <c r="G8" s="23"/>
@@ -3438,17 +3446,17 @@
         <v>8</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>485</v>
+        <v>472</v>
       </c>
       <c r="C9" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Crystallized</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>484</v>
+        <v>471</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="F9" s="25"/>
       <c r="G9" s="25"/>
@@ -3466,17 +3474,17 @@
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>482</v>
+        <v>469</v>
       </c>
       <c r="C10" s="23" t="str">
         <f t="shared" si="0"/>
         <v>Bleeding</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>480</v>
+        <v>467</v>
       </c>
       <c r="F10" s="23"/>
       <c r="G10" s="23"/>
@@ -3564,34 +3572,34 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="F1" s="19" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="G1" s="20" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="H1" s="19" t="s">
-        <v>479</v>
+        <v>466</v>
       </c>
       <c r="I1" s="19" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="J1" s="18" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="K1" s="18"/>
       <c r="L1" s="19"/>
@@ -3606,14 +3614,14 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
-        <v>478</v>
+        <v>465</v>
       </c>
       <c r="B2" s="15" t="str">
         <f t="shared" ref="B2:B26" si="0">A2</f>
         <v>Rapid Supply</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>477</v>
+        <v>464</v>
       </c>
       <c r="D2" s="15" t="s">
         <v>29</v>
@@ -3621,10 +3629,10 @@
       <c r="E2" s="15"/>
       <c r="F2" s="15"/>
       <c r="G2" s="13" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="I2" s="15" t="s">
         <v>0</v>
@@ -3645,14 +3653,14 @@
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
-        <v>475</v>
+        <v>462</v>
       </c>
       <c r="B3" s="16" t="str">
         <f t="shared" si="0"/>
         <v>Candlelight Sanctuary</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="D3" s="16" t="s">
         <v>29</v>
@@ -3664,10 +3672,10 @@
         <v>1</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="I3" s="16" t="s">
         <v>0</v>
@@ -3688,14 +3696,14 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="B4" s="15" t="str">
         <f t="shared" si="0"/>
         <v>Feedback</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>471</v>
+        <v>458</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>3</v>
@@ -3703,10 +3711,10 @@
       <c r="E4" s="15"/>
       <c r="F4" s="15"/>
       <c r="G4" s="13" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="I4" s="15" t="s">
         <v>169</v>
@@ -3746,10 +3754,10 @@
         <v>2</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="I5" s="16" t="s">
         <v>6</v>
@@ -3770,14 +3778,14 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>469</v>
+        <v>456</v>
       </c>
       <c r="B6" s="15" t="str">
         <f t="shared" si="0"/>
         <v>Reverse Decision</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="D6" s="15" t="s">
         <v>3</v>
@@ -3789,10 +3797,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="I6" s="15" t="s">
         <v>6</v>
@@ -3813,14 +3821,14 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="B7" s="16" t="str">
         <f t="shared" si="0"/>
         <v>Bloody Brawl</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>466</v>
+        <v>453</v>
       </c>
       <c r="D7" s="16" t="s">
         <v>29</v>
@@ -3828,10 +3836,10 @@
       <c r="E7" s="16"/>
       <c r="F7" s="16"/>
       <c r="G7" s="14" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="I7" s="16" t="s">
         <v>20</v>
@@ -3852,14 +3860,14 @@
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="B8" s="15" t="str">
         <f t="shared" si="0"/>
         <v>Battle on All Sides</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>3</v>
@@ -3867,10 +3875,10 @@
       <c r="E8" s="15"/>
       <c r="F8" s="15"/>
       <c r="G8" s="13" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>6</v>
@@ -3891,14 +3899,14 @@
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="B9" s="16" t="str">
         <f t="shared" si="0"/>
         <v>Short Dagger</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="D9" s="16" t="s">
         <v>29</v>
@@ -3906,10 +3914,10 @@
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
       <c r="G9" s="14" t="s">
-        <v>461</v>
+        <v>522</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="I9" s="16" t="s">
         <v>6</v>
@@ -3930,14 +3938,14 @@
     </row>
     <row r="10" spans="1:20" ht="26" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="B10" s="15" t="str">
         <f t="shared" si="0"/>
         <v>Blazing Dance</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>3</v>
@@ -3945,10 +3953,10 @@
       <c r="E10" s="15"/>
       <c r="F10" s="15"/>
       <c r="G10" s="13" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>6</v>
@@ -3969,14 +3977,14 @@
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="B11" s="16" t="str">
         <f t="shared" si="0"/>
         <v>Poisoned Sword</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="D11" s="16" t="s">
         <v>3</v>
@@ -3984,10 +3992,10 @@
       <c r="E11" s="16"/>
       <c r="F11" s="16"/>
       <c r="G11" s="14" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="I11" s="16" t="s">
         <v>6</v>
@@ -4008,14 +4016,14 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="B12" s="15" t="str">
         <f t="shared" si="0"/>
         <v>Mist Shadow Sword</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="D12" s="15" t="s">
         <v>3</v>
@@ -4023,10 +4031,10 @@
       <c r="E12" s="15"/>
       <c r="F12" s="15"/>
       <c r="G12" s="13" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>6</v>
@@ -4047,14 +4055,14 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="B13" s="16" t="str">
         <f t="shared" si="0"/>
         <v>Fight to the Death</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="D13" s="16" t="s">
         <v>3</v>
@@ -4062,10 +4070,10 @@
       <c r="E13" s="16"/>
       <c r="F13" s="16"/>
       <c r="G13" s="14" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="I13" s="16" t="s">
         <v>6</v>
@@ -4086,14 +4094,14 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="B14" s="15" t="str">
         <f t="shared" si="0"/>
         <v>Attract Misfortune</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="D14" s="15" t="s">
         <v>23</v>
@@ -4105,10 +4113,10 @@
         <v>2</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>169</v>
@@ -4129,14 +4137,14 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="B15" s="16" t="str">
         <f t="shared" si="0"/>
         <v>Painful Thorns</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="D15" s="16" t="s">
         <v>29</v>
@@ -4144,13 +4152,13 @@
       <c r="E15" s="16"/>
       <c r="F15" s="16"/>
       <c r="G15" s="14" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="J15" s="16">
         <v>5</v>
@@ -4168,14 +4176,14 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="B16" s="15" t="str">
         <f t="shared" si="0"/>
         <v>Crystal Armor</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>3</v>
@@ -4183,10 +4191,10 @@
       <c r="E16" s="15"/>
       <c r="F16" s="15"/>
       <c r="G16" s="13" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>6</v>
@@ -4207,14 +4215,14 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="B17" s="16" t="str">
         <f t="shared" si="0"/>
         <v>Purification Amulet</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="D17" s="16" t="s">
         <v>3</v>
@@ -4222,10 +4230,10 @@
       <c r="E17" s="16"/>
       <c r="F17" s="16"/>
       <c r="G17" s="14" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="I17" s="16" t="s">
         <v>6</v>
@@ -4246,14 +4254,14 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="B18" s="15" t="str">
         <f t="shared" si="0"/>
         <v>Forest's Breath</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>29</v>
@@ -4265,13 +4273,13 @@
         <v>3</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="H18" s="15" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="J18" s="15">
         <v>0</v>
@@ -4289,14 +4297,14 @@
     </row>
     <row r="19" spans="1:20" ht="26" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="B19" s="16" t="str">
         <f t="shared" si="0"/>
         <v>Cursed Soul's Whisper</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="D19" s="16" t="s">
         <v>29</v>
@@ -4308,10 +4316,10 @@
         <v>2</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="I19" s="16" t="s">
         <v>26</v>
@@ -4332,14 +4340,14 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="B20" s="15" t="str">
         <f t="shared" si="0"/>
         <v>Enlighten</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>29</v>
@@ -4347,13 +4355,13 @@
       <c r="E20" s="15"/>
       <c r="F20" s="15"/>
       <c r="G20" s="13" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="I20" s="15" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="J20" s="15">
         <v>3</v>
@@ -4371,14 +4379,14 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="B21" s="16" t="str">
         <f t="shared" si="0"/>
         <v>Leap Counter</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="D21" s="16" t="s">
         <v>3</v>
@@ -4386,10 +4394,10 @@
       <c r="E21" s="16"/>
       <c r="F21" s="16"/>
       <c r="G21" s="14" t="s">
-        <v>424</v>
+        <v>523</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="I21" s="16" t="s">
         <v>6</v>
@@ -4410,14 +4418,14 @@
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="B22" s="15" t="str">
         <f t="shared" si="0"/>
         <v>Bloodborne Rebirth</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>3</v>
@@ -4429,10 +4437,10 @@
         <v>1</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="H22" s="15" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>6</v>
@@ -4453,14 +4461,14 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="B23" s="16" t="str">
         <f t="shared" si="0"/>
         <v>Flawless Defense</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="D23" s="16" t="s">
         <v>29</v>
@@ -4472,10 +4480,10 @@
         <v>2</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="I23" s="16" t="s">
         <v>6</v>
@@ -4496,14 +4504,14 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="B24" s="15" t="str">
         <f t="shared" si="0"/>
         <v>Territorial Imprisonment</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="D24" s="15" t="s">
         <v>29</v>
@@ -4515,10 +4523,10 @@
         <v>3</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="H24" s="15" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>6</v>
@@ -4539,14 +4547,14 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="B25" s="16" t="str">
         <f t="shared" si="0"/>
         <v>Immovable as a Bell</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="D25" s="16" t="s">
         <v>3</v>
@@ -4554,10 +4562,10 @@
       <c r="E25" s="16"/>
       <c r="F25" s="16"/>
       <c r="G25" s="14" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="I25" s="16" t="s">
         <v>6</v>
@@ -4578,14 +4586,14 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="B26" s="15" t="str">
         <f t="shared" si="0"/>
         <v>Charging Shield</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="D26" s="15" t="s">
         <v>3</v>
@@ -4593,10 +4601,10 @@
       <c r="E26" s="15"/>
       <c r="F26" s="15"/>
       <c r="G26" s="13" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="H26" s="15" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>6</v>
@@ -4968,43 +4976,43 @@
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="N1" s="7"/>
       <c r="O1" s="8"/>
@@ -5025,14 +5033,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="C2" s="3" t="str">
         <f t="shared" ref="C2:C33" si="0">B2</f>
         <v>Save Me!!!</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>3</v>
@@ -5044,11 +5052,11 @@
         <v>1</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="3" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>0</v>
@@ -5078,14 +5086,14 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="C3" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Toy Assembly Line</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>29</v>
@@ -5095,11 +5103,11 @@
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="6" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="I3" s="6"/>
       <c r="J3" s="5" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="K3" s="5"/>
       <c r="L3" s="5">
@@ -5127,14 +5135,14 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="C4" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Castle Guardian</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>3</v>
@@ -5146,11 +5154,11 @@
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="3" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>0</v>
@@ -5180,14 +5188,14 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="C5" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Fight Again</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>3</v>
@@ -5199,11 +5207,11 @@
         <v>1</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="I5" s="6"/>
       <c r="J5" s="5" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>6</v>
@@ -5233,14 +5241,14 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="C6" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Waraxe Dance</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>23</v>
@@ -5250,11 +5258,11 @@
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="4" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="3" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>286</v>
@@ -5284,14 +5292,14 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>373</v>
+        <v>519</v>
       </c>
       <c r="C7" s="5" t="str">
         <f t="shared" si="0"/>
-        <v>Intimidation</v>
+        <v>Time Distortion</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>372</v>
+        <v>520</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>29</v>
@@ -5301,11 +5309,11 @@
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="6" t="s">
-        <v>371</v>
+        <v>521</v>
       </c>
       <c r="I7" s="6"/>
       <c r="J7" s="5" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>6</v>
@@ -5335,14 +5343,14 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="C8" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Void Servant</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>29</v>
@@ -5352,14 +5360,14 @@
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="4" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="3" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="L8" s="3">
         <v>2</v>
@@ -5386,14 +5394,14 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="C9" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Devour the Stars</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>363</v>
+        <v>512</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>23</v>
@@ -5403,14 +5411,14 @@
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="6" t="s">
-        <v>362</v>
+        <v>511</v>
       </c>
       <c r="I9" s="6"/>
       <c r="J9" s="5" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="L9" s="5">
         <v>4</v>
@@ -5437,14 +5445,14 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="C10" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Morphing Remains</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>3</v>
@@ -5454,11 +5462,11 @@
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="4" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="3" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>0</v>
@@ -5488,14 +5496,14 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="C11" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Charge</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>3</v>
@@ -5507,11 +5515,11 @@
         <v>1</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="I11" s="6"/>
       <c r="J11" s="5" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="K11" s="5" t="s">
         <v>6</v>
@@ -5541,14 +5549,14 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>351</v>
+        <v>516</v>
       </c>
       <c r="C12" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Time Reversal</v>
+        <f>B12</f>
+        <v>Time Fasting</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>350</v>
+        <v>517</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>3</v>
@@ -5560,11 +5568,11 @@
         <v>1</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>349</v>
+        <v>518</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="3" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>0</v>
@@ -5589,19 +5597,19 @@
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
     </row>
-    <row r="13" spans="1:26" ht="26" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>347</v>
+        <v>513</v>
       </c>
       <c r="C13" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Cocooning</v>
+        <f>B13</f>
+        <v>Time Reversal</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>346</v>
+        <v>514</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>3</v>
@@ -5613,7 +5621,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>345</v>
+        <v>515</v>
       </c>
       <c r="I13" s="6"/>
       <c r="J13" s="5" t="s">
@@ -5717,7 +5725,7 @@
         <v>337</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="5" t="s">
@@ -6680,7 +6688,7 @@
         <v>261</v>
       </c>
       <c r="C34" s="3" t="str">
-        <f t="shared" ref="C34:C65" si="1">B34</f>
+        <f t="shared" ref="C34:C54" si="1">B34</f>
         <v>Water Warding Incantation</v>
       </c>
       <c r="D34" s="3" t="s">

--- a/Src/Assets/StreamingAssets/Common/Tables/Tables/Skill&Buff.xlsx
+++ b/Src/Assets/StreamingAssets/Common/Tables/Tables/Skill&Buff.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CCA\Src\Assets\StreamingAssets\Common\Tables\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8540D561-90AD-49DE-A00B-1D3C15379C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96BF186A-9405-4210-9764-B53CD1871BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TableExplanation" sheetId="5" r:id="rId1"/>
@@ -1553,9 +1553,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Devour the Stars</t>
-  </si>
-  <si>
     <t>[0,0,1]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2206,6 +2203,10 @@
   </si>
   <si>
     <t>当你防御或反制成功时，你下回合攻击力+1.5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Devouring Stars</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2789,7 +2790,7 @@
     </row>
     <row r="3" spans="1:18" ht="25" x14ac:dyDescent="0.5">
       <c r="A3" s="32" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="Q3" s="31"/>
       <c r="R3" s="31"/>
@@ -2800,56 +2801,56 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="30" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="Q5" s="31"/>
       <c r="R5" s="31"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="30" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q6" s="31"/>
       <c r="R6" s="31"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="30" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="Q7" s="31"/>
       <c r="R7" s="31"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="30" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="Q8" s="31"/>
       <c r="R8" s="31"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="30" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="Q9" s="31"/>
       <c r="R9" s="31"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="30" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Q10" s="31"/>
       <c r="R10" s="31"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="30" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Q11" s="31"/>
       <c r="R11" s="31"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="30" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Q12" s="31"/>
       <c r="R12" s="31"/>
@@ -3240,19 +3241,19 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="28" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E1" s="29" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F1" s="28"/>
       <c r="G1" s="28"/>
@@ -3268,17 +3269,17 @@
         <v>1</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C2" s="23" t="str">
         <f t="shared" ref="C2:C10" si="0">B2</f>
         <v>Diving</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E2" s="24" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F2" s="23"/>
       <c r="G2" s="23"/>
@@ -3294,17 +3295,17 @@
         <v>2</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C3" s="21" t="str">
         <f t="shared" si="0"/>
         <v>Stunned</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="R3" s="27"/>
       <c r="S3" s="27"/>
@@ -3314,17 +3315,17 @@
         <v>3</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C4" s="23" t="str">
         <f t="shared" si="0"/>
         <v>Invincible</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F4" s="23"/>
       <c r="G4" s="23"/>
@@ -3342,17 +3343,17 @@
         <v>4</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C5" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Critical</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F5" s="25"/>
       <c r="G5" s="25"/>
@@ -3370,17 +3371,17 @@
         <v>5</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C6" s="23" t="str">
         <f t="shared" si="0"/>
         <v>Slowed</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F6" s="23"/>
       <c r="G6" s="23"/>
@@ -3398,17 +3399,17 @@
         <v>6</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C7" s="21" t="str">
         <f t="shared" si="0"/>
         <v>Burning</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R7" s="27"/>
       <c r="S7" s="27"/>
@@ -3418,17 +3419,17 @@
         <v>7</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C8" s="23" t="str">
         <f t="shared" si="0"/>
         <v>Cocooned</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F8" s="23"/>
       <c r="G8" s="23"/>
@@ -3446,17 +3447,17 @@
         <v>8</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C9" s="25" t="str">
         <f t="shared" si="0"/>
         <v>Crystallized</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F9" s="25"/>
       <c r="G9" s="25"/>
@@ -3474,17 +3475,17 @@
         <v>9</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C10" s="23" t="str">
         <f t="shared" si="0"/>
         <v>Bleeding</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F10" s="23"/>
       <c r="G10" s="23"/>
@@ -3572,34 +3573,34 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F1" s="19" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G1" s="20" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1" s="19" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="I1" s="19" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="J1" s="18" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="K1" s="18"/>
       <c r="L1" s="19"/>
@@ -3614,14 +3615,14 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B2" s="15" t="str">
         <f t="shared" ref="B2:B26" si="0">A2</f>
         <v>Rapid Supply</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D2" s="15" t="s">
         <v>29</v>
@@ -3629,10 +3630,10 @@
       <c r="E2" s="15"/>
       <c r="F2" s="15"/>
       <c r="G2" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I2" s="15" t="s">
         <v>0</v>
@@ -3653,14 +3654,14 @@
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B3" s="16" t="str">
         <f t="shared" si="0"/>
         <v>Candlelight Sanctuary</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D3" s="16" t="s">
         <v>29</v>
@@ -3672,10 +3673,10 @@
         <v>1</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I3" s="16" t="s">
         <v>0</v>
@@ -3696,14 +3697,14 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B4" s="15" t="str">
         <f t="shared" si="0"/>
         <v>Feedback</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>3</v>
@@ -3711,10 +3712,10 @@
       <c r="E4" s="15"/>
       <c r="F4" s="15"/>
       <c r="G4" s="13" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I4" s="15" t="s">
         <v>169</v>
@@ -3754,10 +3755,10 @@
         <v>2</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="I5" s="16" t="s">
         <v>6</v>
@@ -3778,14 +3779,14 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B6" s="15" t="str">
         <f t="shared" si="0"/>
         <v>Reverse Decision</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D6" s="15" t="s">
         <v>3</v>
@@ -3797,10 +3798,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I6" s="15" t="s">
         <v>6</v>
@@ -3821,14 +3822,14 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B7" s="16" t="str">
         <f t="shared" si="0"/>
         <v>Bloody Brawl</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D7" s="16" t="s">
         <v>29</v>
@@ -3836,10 +3837,10 @@
       <c r="E7" s="16"/>
       <c r="F7" s="16"/>
       <c r="G7" s="14" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="I7" s="16" t="s">
         <v>20</v>
@@ -3860,14 +3861,14 @@
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B8" s="15" t="str">
         <f t="shared" si="0"/>
         <v>Battle on All Sides</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>3</v>
@@ -3875,10 +3876,10 @@
       <c r="E8" s="15"/>
       <c r="F8" s="15"/>
       <c r="G8" s="13" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>6</v>
@@ -3899,14 +3900,14 @@
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B9" s="16" t="str">
         <f t="shared" si="0"/>
         <v>Short Dagger</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D9" s="16" t="s">
         <v>29</v>
@@ -3914,10 +3915,10 @@
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
       <c r="G9" s="14" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="I9" s="16" t="s">
         <v>6</v>
@@ -3938,14 +3939,14 @@
     </row>
     <row r="10" spans="1:20" ht="26" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B10" s="15" t="str">
         <f t="shared" si="0"/>
         <v>Blazing Dance</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>3</v>
@@ -3953,10 +3954,10 @@
       <c r="E10" s="15"/>
       <c r="F10" s="15"/>
       <c r="G10" s="13" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>6</v>
@@ -3977,14 +3978,14 @@
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B11" s="16" t="str">
         <f t="shared" si="0"/>
         <v>Poisoned Sword</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D11" s="16" t="s">
         <v>3</v>
@@ -3992,10 +3993,10 @@
       <c r="E11" s="16"/>
       <c r="F11" s="16"/>
       <c r="G11" s="14" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="I11" s="16" t="s">
         <v>6</v>
@@ -4016,14 +4017,14 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B12" s="15" t="str">
         <f t="shared" si="0"/>
         <v>Mist Shadow Sword</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D12" s="15" t="s">
         <v>3</v>
@@ -4031,10 +4032,10 @@
       <c r="E12" s="15"/>
       <c r="F12" s="15"/>
       <c r="G12" s="13" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>6</v>
@@ -4055,14 +4056,14 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B13" s="16" t="str">
         <f t="shared" si="0"/>
         <v>Fight to the Death</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D13" s="16" t="s">
         <v>3</v>
@@ -4070,10 +4071,10 @@
       <c r="E13" s="16"/>
       <c r="F13" s="16"/>
       <c r="G13" s="14" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I13" s="16" t="s">
         <v>6</v>
@@ -4094,14 +4095,14 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B14" s="15" t="str">
         <f t="shared" si="0"/>
         <v>Attract Misfortune</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D14" s="15" t="s">
         <v>23</v>
@@ -4113,10 +4114,10 @@
         <v>2</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>169</v>
@@ -4137,14 +4138,14 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B15" s="16" t="str">
         <f t="shared" si="0"/>
         <v>Painful Thorns</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D15" s="16" t="s">
         <v>29</v>
@@ -4152,13 +4153,13 @@
       <c r="E15" s="16"/>
       <c r="F15" s="16"/>
       <c r="G15" s="14" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="J15" s="16">
         <v>5</v>
@@ -4176,14 +4177,14 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B16" s="15" t="str">
         <f t="shared" si="0"/>
         <v>Crystal Armor</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>3</v>
@@ -4191,10 +4192,10 @@
       <c r="E16" s="15"/>
       <c r="F16" s="15"/>
       <c r="G16" s="13" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>6</v>
@@ -4215,14 +4216,14 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B17" s="16" t="str">
         <f t="shared" si="0"/>
         <v>Purification Amulet</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D17" s="16" t="s">
         <v>3</v>
@@ -4230,10 +4231,10 @@
       <c r="E17" s="16"/>
       <c r="F17" s="16"/>
       <c r="G17" s="14" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I17" s="16" t="s">
         <v>6</v>
@@ -4254,14 +4255,14 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B18" s="15" t="str">
         <f t="shared" si="0"/>
         <v>Forest's Breath</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>29</v>
@@ -4273,13 +4274,13 @@
         <v>3</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H18" s="15" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J18" s="15">
         <v>0</v>
@@ -4297,14 +4298,14 @@
     </row>
     <row r="19" spans="1:20" ht="26" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B19" s="16" t="str">
         <f t="shared" si="0"/>
         <v>Cursed Soul's Whisper</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D19" s="16" t="s">
         <v>29</v>
@@ -4316,10 +4317,10 @@
         <v>2</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I19" s="16" t="s">
         <v>26</v>
@@ -4340,14 +4341,14 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B20" s="15" t="str">
         <f t="shared" si="0"/>
         <v>Enlighten</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>29</v>
@@ -4355,13 +4356,13 @@
       <c r="E20" s="15"/>
       <c r="F20" s="15"/>
       <c r="G20" s="13" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H20" s="15" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I20" s="15" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J20" s="15">
         <v>3</v>
@@ -4379,14 +4380,14 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B21" s="16" t="str">
         <f t="shared" si="0"/>
         <v>Leap Counter</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D21" s="16" t="s">
         <v>3</v>
@@ -4394,10 +4395,10 @@
       <c r="E21" s="16"/>
       <c r="F21" s="16"/>
       <c r="G21" s="14" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I21" s="16" t="s">
         <v>6</v>
@@ -4418,14 +4419,14 @@
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B22" s="15" t="str">
         <f t="shared" si="0"/>
         <v>Bloodborne Rebirth</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>3</v>
@@ -4437,10 +4438,10 @@
         <v>1</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H22" s="15" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>6</v>
@@ -4461,14 +4462,14 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B23" s="16" t="str">
         <f t="shared" si="0"/>
         <v>Flawless Defense</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D23" s="16" t="s">
         <v>29</v>
@@ -4480,10 +4481,10 @@
         <v>2</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I23" s="16" t="s">
         <v>6</v>
@@ -4504,14 +4505,14 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B24" s="15" t="str">
         <f t="shared" si="0"/>
         <v>Territorial Imprisonment</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D24" s="15" t="s">
         <v>29</v>
@@ -4523,10 +4524,10 @@
         <v>3</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H24" s="15" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>6</v>
@@ -4547,14 +4548,14 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B25" s="16" t="str">
         <f t="shared" si="0"/>
         <v>Immovable as a Bell</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D25" s="16" t="s">
         <v>3</v>
@@ -4562,10 +4563,10 @@
       <c r="E25" s="16"/>
       <c r="F25" s="16"/>
       <c r="G25" s="14" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I25" s="16" t="s">
         <v>6</v>
@@ -4586,14 +4587,14 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B26" s="15" t="str">
         <f t="shared" si="0"/>
         <v>Charging Shield</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D26" s="15" t="s">
         <v>3</v>
@@ -4601,10 +4602,10 @@
       <c r="E26" s="15"/>
       <c r="F26" s="15"/>
       <c r="G26" s="13" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H26" s="15" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>6</v>
@@ -4976,43 +4977,43 @@
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="N1" s="7"/>
       <c r="O1" s="8"/>
@@ -5033,14 +5034,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C2" s="3" t="str">
         <f t="shared" ref="C2:C33" si="0">B2</f>
         <v>Save Me!!!</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>3</v>
@@ -5052,11 +5053,11 @@
         <v>1</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>0</v>
@@ -5086,14 +5087,14 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C3" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Toy Assembly Line</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>29</v>
@@ -5103,11 +5104,11 @@
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I3" s="6"/>
       <c r="J3" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="K3" s="5"/>
       <c r="L3" s="5">
@@ -5135,14 +5136,14 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C4" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Castle Guardian</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>3</v>
@@ -5154,11 +5155,11 @@
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>0</v>
@@ -5188,14 +5189,14 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C5" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Fight Again</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>3</v>
@@ -5207,11 +5208,11 @@
         <v>1</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I5" s="6"/>
       <c r="J5" s="5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>6</v>
@@ -5241,14 +5242,14 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C6" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Waraxe Dance</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>23</v>
@@ -5258,11 +5259,11 @@
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>286</v>
@@ -5292,14 +5293,14 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C7" s="5" t="str">
         <f t="shared" si="0"/>
         <v>Time Distortion</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>29</v>
@@ -5309,11 +5310,11 @@
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="6" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="I7" s="6"/>
       <c r="J7" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>6</v>
@@ -5343,14 +5344,14 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C8" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Void Servant</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>29</v>
@@ -5360,14 +5361,14 @@
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="L8" s="3">
         <v>2</v>
@@ -5394,14 +5395,14 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>356</v>
+        <v>523</v>
       </c>
       <c r="C9" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>Devour the Stars</v>
+        <f>B9</f>
+        <v>Devouring Stars</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>23</v>
@@ -5411,7 +5412,7 @@
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="6" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="I9" s="6"/>
       <c r="J9" s="5" t="s">
@@ -5549,14 +5550,14 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C12" s="3" t="str">
         <f>B12</f>
         <v>Time Fasting</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>3</v>
@@ -5568,7 +5569,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="3" t="s">
@@ -5602,14 +5603,14 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C13" s="5" t="str">
         <f>B13</f>
         <v>Time Reversal</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>3</v>
@@ -5621,7 +5622,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="I13" s="6"/>
       <c r="J13" s="5" t="s">
@@ -5725,7 +5726,7 @@
         <v>337</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="5" t="s">

--- a/Src/Assets/StreamingAssets/Common/Tables/Tables/Skill&Buff.xlsx
+++ b/Src/Assets/StreamingAssets/Common/Tables/Tables/Skill&Buff.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CCA\Src\Assets\StreamingAssets\Common\Tables\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1DF9684-2328-418A-9AF3-EE92EF8DFFAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F490D4-FB05-4BEB-B544-D4D66E42A256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MonsterSkill" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="473">
   <si>
     <t>[0,0,0]</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -4543,24 +4543,9 @@
     <t>无</t>
   </si>
   <si>
-    <t>Enlightenment on High Fort2</t>
-  </si>
-  <si>
-    <t>Enlightenment on High Fort1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">当你的刀剑类攻击命中一目标时，叠加一点Combo，受伤则失去所有Combo                                                                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">每有一层Combo，你的攻击力+1，刀剑行动额外执行一次                                                                         </t>
-  </si>
-  <si>
     <t>高寨悟道</t>
   </si>
   <si>
-    <t>高寨悟道，连击+1</t>
-  </si>
-  <si>
     <t>回合开始时，你获得玩家的所有剑，玩家失去所有子弹</t>
   </si>
   <si>
@@ -4597,12 +4582,6 @@
     <t>Judgement</t>
   </si>
   <si>
-    <t>Adjudication</t>
-  </si>
-  <si>
-    <t>裁决</t>
-  </si>
-  <si>
     <r>
       <t>替代行动,令玩家下一回合无法使用</t>
     </r>
@@ -4645,14 +4624,11 @@
     <t>CD好了就用</t>
   </si>
   <si>
-    <t>Tactical Turtle2</t>
-  </si>
-  <si>
-    <t>Tactical Turtle1</t>
-  </si>
-  <si>
-    <r>
-      <t>当你受到来自</t>
+    <t>使用此技能后的2回合内，你方单位受到的伤害于技能结束时一次性结算，所结算伤害总量-2</t>
+  </si>
+  <si>
+    <r>
+      <t>本场战斗余下回合中，你的</t>
     </r>
     <r>
       <rPr>
@@ -4674,84 +4650,39 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>与</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>进攻技能</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>的伤害时，受伤-1。受伤时进入龟缩状态</t>
-    </r>
-  </si>
-  <si>
-    <t>使用此技能后的2回合内，你方单位受到的伤害于技能结束时一次性结算，所结算伤害总量-2</t>
-  </si>
-  <si>
-    <t>你力量-2，龟缩状态无法攻击</t>
-  </si>
-  <si>
-    <r>
-      <t>本场战斗余下回合中，你的</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>进攻行动</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
       <t>无法被进攻抵消。攻击造成伤害使得目标力量-1</t>
     </r>
   </si>
   <si>
-    <t>Ready to Beat Down</t>
-  </si>
-  <si>
-    <t>开始殴打</t>
-  </si>
-  <si>
-    <t>本场战斗余下回合中，你进入殴打状态</t>
-  </si>
-  <si>
-    <t>好了就立刻用</t>
-  </si>
-  <si>
     <t>[0,1,0]</t>
   </si>
   <si>
-    <t>替代行动，我方所有单位接下来2回合行动消耗-1</t>
-  </si>
-  <si>
-    <t>[0,0,5]</t>
+    <t>替代行动，我方所有单位接下来2回合行动消耗资源时回复一点体力</t>
+  </si>
+  <si>
+    <t>颂威</t>
+  </si>
+  <si>
+    <t>Ode to Majesty</t>
+  </si>
+  <si>
+    <t>Tactical Turtle</t>
+  </si>
+  <si>
+    <t>你失去2层力量，受到伤害-1。当你受到来自进攻行动与进攻技能的伤害时，你下一回合无法使用进攻与特殊行动且不受伤害</t>
+  </si>
+  <si>
+    <t xml:space="preserve">当你的刀剑类攻击命中一目标时，叠加一点Combo，受伤则失去所有Combo；每有一层Combo，你的攻击力+1，刀剑行动额外执行一次                                                                          </t>
+  </si>
+  <si>
+    <t>Enlightenment on High Fort</t>
+  </si>
+  <si>
+    <t>[0,2,5]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Strength</t>
   </si>
 </sst>
 </file>
@@ -4872,7 +4803,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -5231,13 +5162,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -5444,6 +5384,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5792,7 +5735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8583E483-2AE6-40BE-8AEB-869DA91BBB12}">
-  <dimension ref="A1:X99"/>
+  <dimension ref="A1:X96"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="24.81640625" style="1" customWidth="1"/>
@@ -6477,7 +6420,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="H14" s="16" t="s">
         <v>449</v>
@@ -6509,13 +6452,13 @@
     </row>
     <row r="15" spans="1:24" ht="70" customHeight="1">
       <c r="A15" s="9" t="s">
-        <v>452</v>
+        <v>470</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>452</v>
+        <v>470</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>2</v>
@@ -6527,7 +6470,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>453</v>
+        <v>469</v>
       </c>
       <c r="H15" s="11" t="s">
         <v>450</v>
@@ -6557,41 +6500,41 @@
       <c r="W15" s="5"/>
       <c r="X15" s="5"/>
     </row>
-    <row r="16" spans="1:24" ht="70" customHeight="1">
-      <c r="A16" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="C16" s="9" t="s">
+    <row r="16" spans="1:24" ht="70" customHeight="1" thickBot="1">
+      <c r="A16" s="65" t="s">
+        <v>453</v>
+      </c>
+      <c r="B16" s="65" t="s">
+        <v>453</v>
+      </c>
+      <c r="C16" s="65" t="s">
+        <v>454</v>
+      </c>
+      <c r="D16" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="65" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" s="65">
+        <v>0</v>
+      </c>
+      <c r="G16" s="66" t="s">
         <v>455</v>
       </c>
-      <c r="D16" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E16" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F16" s="9">
-        <v>0</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>454</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>450</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="J16" s="9" t="s">
+      <c r="H16" s="67" t="s">
+        <v>457</v>
+      </c>
+      <c r="I16" s="68" t="s">
+        <v>456</v>
+      </c>
+      <c r="J16" s="65" t="s">
         <v>5</v>
       </c>
-      <c r="K16" s="9">
-        <v>5</v>
-      </c>
-      <c r="L16" s="13" t="b">
+      <c r="K16" s="65">
+        <v>0</v>
+      </c>
+      <c r="L16" s="69" t="b">
         <v>0</v>
       </c>
       <c r="M16" s="5"/>
@@ -6605,43 +6548,42 @@
       <c r="U16" s="5"/>
       <c r="V16" s="5"/>
       <c r="W16" s="5"/>
-      <c r="X16" s="5"/>
     </row>
-    <row r="17" spans="1:24" ht="70" customHeight="1" thickBot="1">
-      <c r="A17" s="65" t="s">
-        <v>458</v>
-      </c>
-      <c r="B17" s="65" t="s">
-        <v>458</v>
-      </c>
-      <c r="C17" s="65" t="s">
-        <v>459</v>
-      </c>
-      <c r="D17" s="65" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="65" t="b">
-        <v>0</v>
-      </c>
-      <c r="F17" s="65">
-        <v>0</v>
-      </c>
-      <c r="G17" s="66" t="s">
+    <row r="17" spans="1:24" ht="15" thickTop="1">
+      <c r="A17" s="31" t="s">
+        <v>466</v>
+      </c>
+      <c r="B17" s="31" t="s">
+        <v>466</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>465</v>
+      </c>
+      <c r="D17" s="31" t="s">
+        <v>412</v>
+      </c>
+      <c r="E17" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="F17" s="31">
+        <v>0</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="H17" s="32" t="s">
         <v>460</v>
       </c>
-      <c r="H17" s="67" t="s">
-        <v>462</v>
-      </c>
-      <c r="I17" s="68" t="s">
-        <v>461</v>
-      </c>
-      <c r="J17" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="K17" s="65">
-        <v>0</v>
-      </c>
-      <c r="L17" s="69" t="b">
+      <c r="I17" s="33" t="s">
+        <v>243</v>
+      </c>
+      <c r="J17" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="K17" s="31">
+        <v>4</v>
+      </c>
+      <c r="L17" s="34" t="b">
         <v>0</v>
       </c>
       <c r="M17" s="5"/>
@@ -6655,219 +6597,220 @@
       <c r="U17" s="5"/>
       <c r="V17" s="5"/>
       <c r="W17" s="5"/>
+      <c r="X17" s="5"/>
     </row>
-    <row r="18" spans="1:24" ht="15" thickTop="1">
-      <c r="A18" s="31" t="s">
-        <v>464</v>
-      </c>
-      <c r="B18" s="31" t="s">
-        <v>464</v>
-      </c>
-      <c r="C18" s="31" t="s">
-        <v>465</v>
-      </c>
-      <c r="D18" s="31" t="s">
+    <row r="18" spans="1:24" ht="46" customHeight="1">
+      <c r="A18" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="D18" s="14" t="s">
         <v>412</v>
       </c>
-      <c r="E18" s="31" t="b">
-        <v>0</v>
-      </c>
-      <c r="F18" s="31">
-        <v>0</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>479</v>
-      </c>
-      <c r="H18" s="32" t="s">
+      <c r="E18" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="15" t="s">
+        <v>459</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>460</v>
+      </c>
+      <c r="I18" s="17" t="s">
+        <v>241</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="K18" s="14">
+        <v>2</v>
+      </c>
+      <c r="L18" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+      <c r="S18" s="3"/>
+      <c r="T18" s="3"/>
+      <c r="U18" s="3"/>
+      <c r="V18" s="3"/>
+      <c r="W18" s="3"/>
+      <c r="X18" s="3"/>
+    </row>
+    <row r="19" spans="1:24">
+      <c r="A19" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E19" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" s="9">
+        <v>0</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="K19" s="9">
+        <v>0</v>
+      </c>
+      <c r="L19" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="5"/>
+      <c r="S19" s="5"/>
+      <c r="T19" s="5"/>
+      <c r="U19" s="5"/>
+      <c r="V19" s="5"/>
+      <c r="W19" s="5"/>
+      <c r="X19" s="5"/>
+    </row>
+    <row r="20" spans="1:24" ht="39">
+      <c r="A20" s="14" t="s">
         <v>467</v>
       </c>
-      <c r="I18" s="33" t="s">
-        <v>243</v>
-      </c>
-      <c r="J18" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="K18" s="31">
-        <v>4</v>
-      </c>
-      <c r="L18" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
-      <c r="R18" s="5"/>
-      <c r="S18" s="5"/>
-      <c r="T18" s="5"/>
-      <c r="U18" s="5"/>
-      <c r="V18" s="5"/>
-      <c r="W18" s="5"/>
-      <c r="X18" s="5"/>
-    </row>
-    <row r="19" spans="1:24" ht="46" customHeight="1">
-      <c r="A19" s="14" t="s">
-        <v>463</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>463</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>242</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>412</v>
-      </c>
-      <c r="E19" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F19" s="14">
-        <v>0</v>
-      </c>
-      <c r="G19" s="15" t="s">
-        <v>466</v>
-      </c>
-      <c r="H19" s="16" t="s">
+      <c r="B20" s="14" t="s">
         <v>467</v>
       </c>
-      <c r="I19" s="17" t="s">
-        <v>241</v>
-      </c>
-      <c r="J19" s="14" t="s">
-        <v>478</v>
-      </c>
-      <c r="K19" s="14">
+      <c r="C20" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="D20" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="L19" s="18" t="b">
+      <c r="E20" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14">
+        <v>0</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>468</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="I20" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="J20" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="14">
+        <v>0</v>
+      </c>
+      <c r="L20" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="1:24">
-      <c r="A20" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E20" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F20" s="9">
-        <v>0</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>287</v>
-      </c>
-      <c r="I20" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="K20" s="9">
-        <v>0</v>
-      </c>
-      <c r="L20" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="5"/>
-      <c r="S20" s="5"/>
-      <c r="T20" s="5"/>
-      <c r="U20" s="5"/>
-      <c r="V20" s="5"/>
-      <c r="W20" s="5"/>
-      <c r="X20" s="5"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="3"/>
+      <c r="V20" s="3"/>
+      <c r="W20" s="3"/>
+      <c r="X20" s="3"/>
     </row>
     <row r="21" spans="1:24">
-      <c r="A21" s="14" t="s">
-        <v>469</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>469</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="D21" s="14" t="s">
+      <c r="A21" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E21" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F21" s="14">
-        <v>0</v>
-      </c>
-      <c r="G21" s="15" t="s">
-        <v>472</v>
-      </c>
-      <c r="H21" s="16" t="s">
+      <c r="E21" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" s="9">
+        <v>0</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="H21" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="I21" s="17" t="s">
-        <v>236</v>
-      </c>
-      <c r="J21" s="14" t="s">
+      <c r="I21" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="J21" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="K21" s="14">
-        <v>0</v>
-      </c>
-      <c r="L21" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-      <c r="P21" s="3"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="3"/>
-      <c r="S21" s="3"/>
-      <c r="T21" s="3"/>
-      <c r="U21" s="3"/>
-      <c r="V21" s="3"/>
-      <c r="W21" s="3"/>
-      <c r="X21" s="3"/>
+      <c r="K21" s="9">
+        <v>0</v>
+      </c>
+      <c r="L21" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="5"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+      <c r="W21" s="5"/>
+      <c r="X21" s="5"/>
     </row>
     <row r="22" spans="1:24" ht="26">
       <c r="A22" s="14" t="s">
-        <v>468</v>
+        <v>232</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>468</v>
+        <v>232</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="E22" s="14" t="b">
         <v>0</v>
@@ -6876,22 +6819,22 @@
         <v>0</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>287</v>
+        <v>450</v>
       </c>
       <c r="I22" s="17" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>5</v>
+        <v>471</v>
       </c>
       <c r="K22" s="14">
         <v>0</v>
       </c>
       <c r="L22" s="18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
@@ -6906,33 +6849,33 @@
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" ht="26">
       <c r="A23" s="9" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>2</v>
       </c>
       <c r="E23" s="9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H23" s="11" t="s">
         <v>287</v>
       </c>
       <c r="I23" s="12" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="J23" s="9" t="s">
         <v>5</v>
@@ -6956,18 +6899,18 @@
       <c r="W23" s="5"/>
       <c r="X23" s="5"/>
     </row>
-    <row r="24" spans="1:24" ht="26">
+    <row r="24" spans="1:24" ht="39">
       <c r="A24" s="14" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="E24" s="14" t="b">
         <v>0</v>
@@ -6976,19 +6919,19 @@
         <v>0</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>473</v>
+        <v>312</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>450</v>
+        <v>313</v>
       </c>
       <c r="I24" s="17" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="J24" s="14" t="s">
         <v>5</v>
       </c>
       <c r="K24" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24" s="18" t="b">
         <v>0</v>
@@ -7006,3623 +6949,3473 @@
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
     </row>
-    <row r="25" spans="1:24">
-      <c r="A25" s="14" t="s">
-        <v>474</v>
-      </c>
-      <c r="B25" s="14" t="s">
-        <v>474</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>475</v>
-      </c>
-      <c r="D25" s="14" t="s">
+    <row r="25" spans="1:24" ht="26">
+      <c r="A25" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="D25" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E25" s="14" t="b">
+      <c r="E25" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="F25" s="14">
+      <c r="F25" s="9">
         <v>1</v>
       </c>
-      <c r="G25" s="15" t="s">
-        <v>476</v>
-      </c>
-      <c r="H25" s="16" t="s">
-        <v>477</v>
-      </c>
-      <c r="I25" s="17" t="s">
-        <v>230</v>
-      </c>
-      <c r="J25" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="K25" s="14">
-        <v>0</v>
-      </c>
-      <c r="L25" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
-      <c r="U25" s="3"/>
-      <c r="V25" s="3"/>
-      <c r="W25" s="3"/>
-      <c r="X25" s="3"/>
+      <c r="G25" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="H25" s="35" t="s">
+        <v>314</v>
+      </c>
+      <c r="I25" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="K25" s="9">
+        <v>0</v>
+      </c>
+      <c r="L25" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="5"/>
+      <c r="R25" s="5"/>
+      <c r="S25" s="5"/>
+      <c r="T25" s="5"/>
+      <c r="U25" s="5"/>
+      <c r="V25" s="5"/>
+      <c r="W25" s="5"/>
+      <c r="X25" s="5"/>
     </row>
-    <row r="26" spans="1:24" ht="26">
-      <c r="A26" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E26" s="9" t="b">
+    <row r="26" spans="1:24">
+      <c r="A26" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="14">
         <v>1</v>
       </c>
-      <c r="G26" s="10" t="s">
-        <v>311</v>
-      </c>
-      <c r="H26" s="11" t="s">
-        <v>287</v>
-      </c>
-      <c r="I26" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="J26" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="K26" s="9">
-        <v>0</v>
-      </c>
-      <c r="L26" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M26" s="5"/>
-      <c r="N26" s="5"/>
-      <c r="O26" s="5"/>
-      <c r="P26" s="5"/>
-      <c r="Q26" s="5"/>
-      <c r="R26" s="5"/>
-      <c r="S26" s="5"/>
-      <c r="T26" s="5"/>
-      <c r="U26" s="5"/>
-      <c r="V26" s="5"/>
-      <c r="W26" s="5"/>
-      <c r="X26" s="5"/>
+      <c r="G26" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="H26" s="36" t="s">
+        <v>316</v>
+      </c>
+      <c r="I26" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="J26" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="K26" s="14">
+        <v>0</v>
+      </c>
+      <c r="L26" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3"/>
+      <c r="U26" s="3"/>
+      <c r="V26" s="3"/>
+      <c r="W26" s="3"/>
+      <c r="X26" s="3"/>
     </row>
     <row r="27" spans="1:24" ht="39">
-      <c r="A27" s="14" t="s">
-        <v>226</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>226</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="D27" s="14" t="s">
+      <c r="A27" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D27" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E27" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F27" s="14">
-        <v>0</v>
-      </c>
-      <c r="G27" s="15" t="s">
-        <v>312</v>
-      </c>
-      <c r="H27" s="16" t="s">
-        <v>313</v>
-      </c>
-      <c r="I27" s="17" t="s">
-        <v>224</v>
-      </c>
-      <c r="J27" s="14" t="s">
+      <c r="E27" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" s="9">
+        <v>0</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="I27" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="J27" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="K27" s="14">
+      <c r="K27" s="9">
+        <v>0</v>
+      </c>
+      <c r="L27" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5"/>
+      <c r="R27" s="5"/>
+      <c r="S27" s="5"/>
+      <c r="T27" s="5"/>
+      <c r="U27" s="5"/>
+      <c r="V27" s="5"/>
+      <c r="W27" s="5"/>
+      <c r="X27" s="5"/>
+    </row>
+    <row r="28" spans="1:24" ht="52">
+      <c r="A28" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="D28" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="L27" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
-      <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="3"/>
-      <c r="S27" s="3"/>
-      <c r="T27" s="3"/>
-      <c r="U27" s="3"/>
-      <c r="V27" s="3"/>
-      <c r="W27" s="3"/>
-      <c r="X27" s="3"/>
+      <c r="E28" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F28" s="14">
+        <v>0</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="H28" s="16" t="s">
+        <v>320</v>
+      </c>
+      <c r="I28" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="J28" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="K28" s="14">
+        <v>0</v>
+      </c>
+      <c r="L28" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3"/>
+      <c r="U28" s="3"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="3"/>
+      <c r="X28" s="3"/>
     </row>
-    <row r="28" spans="1:24" ht="26">
-      <c r="A28" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E28" s="9" t="b">
+    <row r="29" spans="1:24" ht="52">
+      <c r="A29" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E29" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29" s="9">
+        <v>0</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="I29" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="K29" s="9">
+        <v>0</v>
+      </c>
+      <c r="L29" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="5"/>
+      <c r="R29" s="5"/>
+      <c r="S29" s="5"/>
+      <c r="T29" s="5"/>
+      <c r="U29" s="5"/>
+      <c r="V29" s="5"/>
+      <c r="W29" s="5"/>
+      <c r="X29" s="5"/>
+    </row>
+    <row r="30" spans="1:24" ht="78">
+      <c r="A30" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E30" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" s="14">
+        <v>0</v>
+      </c>
+      <c r="G30" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="I30" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="J30" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="K30" s="14">
+        <v>0</v>
+      </c>
+      <c r="L30" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+      <c r="S30" s="3"/>
+      <c r="T30" s="3"/>
+      <c r="U30" s="3"/>
+      <c r="V30" s="3"/>
+      <c r="W30" s="3"/>
+      <c r="X30" s="3"/>
+    </row>
+    <row r="31" spans="1:24" ht="39">
+      <c r="A31" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E31" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F31" s="9">
+        <v>0</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="I31" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="K31" s="9">
+        <v>0</v>
+      </c>
+      <c r="L31" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5"/>
+      <c r="R31" s="5"/>
+      <c r="S31" s="5"/>
+      <c r="T31" s="5"/>
+      <c r="U31" s="5"/>
+      <c r="V31" s="5"/>
+      <c r="W31" s="5"/>
+      <c r="X31" s="5"/>
+    </row>
+    <row r="32" spans="1:24" ht="65.5" thickBot="1">
+      <c r="A32" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="B32" s="37" t="s">
+        <v>201</v>
+      </c>
+      <c r="C32" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="D32" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="E32" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="F32" s="37">
+        <v>0</v>
+      </c>
+      <c r="G32" s="38" t="s">
+        <v>327</v>
+      </c>
+      <c r="H32" s="39" t="s">
+        <v>287</v>
+      </c>
+      <c r="I32" s="40" t="s">
+        <v>199</v>
+      </c>
+      <c r="J32" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="37">
+        <v>0</v>
+      </c>
+      <c r="L32" s="41" t="b">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
+      <c r="S32" s="3"/>
+      <c r="T32" s="3"/>
+      <c r="U32" s="3"/>
+      <c r="V32" s="3"/>
+      <c r="W32" s="3"/>
+      <c r="X32" s="3"/>
+    </row>
+    <row r="33" spans="1:24" ht="26.5" thickTop="1">
+      <c r="A33" s="31" t="s">
+        <v>328</v>
+      </c>
+      <c r="B33" s="31" t="s">
+        <v>328</v>
+      </c>
+      <c r="C33" s="31" t="s">
+        <v>198</v>
+      </c>
+      <c r="D33" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" s="31" t="b">
+        <v>0</v>
+      </c>
+      <c r="F33" s="31">
+        <v>0</v>
+      </c>
+      <c r="G33" s="42" t="s">
+        <v>329</v>
+      </c>
+      <c r="H33" s="32" t="s">
+        <v>330</v>
+      </c>
+      <c r="I33" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="J33" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="K33" s="31">
+        <v>3</v>
+      </c>
+      <c r="L33" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="5"/>
+      <c r="R33" s="5"/>
+      <c r="S33" s="5"/>
+      <c r="T33" s="5"/>
+      <c r="U33" s="5"/>
+      <c r="V33" s="5"/>
+      <c r="W33" s="5"/>
+      <c r="X33" s="5"/>
+    </row>
+    <row r="34" spans="1:24">
+      <c r="A34" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E34" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F34" s="14">
+        <v>0</v>
+      </c>
+      <c r="G34" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="H34" s="16"/>
+      <c r="I34" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="J34" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="K34" s="14">
+        <v>0</v>
+      </c>
+      <c r="L34" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="F28" s="9">
+      <c r="M34" s="3"/>
+      <c r="N34" s="3"/>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="3"/>
+      <c r="R34" s="3"/>
+      <c r="S34" s="3"/>
+      <c r="T34" s="3"/>
+      <c r="U34" s="3"/>
+      <c r="V34" s="3"/>
+      <c r="W34" s="3"/>
+      <c r="X34" s="3"/>
+    </row>
+    <row r="35" spans="1:24" ht="26">
+      <c r="A35" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E35" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F35" s="9">
+        <v>0</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="H35" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="I35" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="K35" s="9">
+        <v>0</v>
+      </c>
+      <c r="L35" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="G28" s="10" t="s">
-        <v>471</v>
-      </c>
-      <c r="H28" s="35" t="s">
-        <v>314</v>
-      </c>
-      <c r="I28" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="J28" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="K28" s="9">
-        <v>0</v>
-      </c>
-      <c r="L28" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="5"/>
-      <c r="R28" s="5"/>
-      <c r="S28" s="5"/>
-      <c r="T28" s="5"/>
-      <c r="U28" s="5"/>
-      <c r="V28" s="5"/>
-      <c r="W28" s="5"/>
-      <c r="X28" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="5"/>
+      <c r="R35" s="5"/>
+      <c r="S35" s="5"/>
+      <c r="T35" s="5"/>
+      <c r="U35" s="5"/>
+      <c r="V35" s="5"/>
+      <c r="W35" s="5"/>
+      <c r="X35" s="5"/>
     </row>
-    <row r="29" spans="1:24">
-      <c r="A29" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>219</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="E29" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="F29" s="14">
-        <v>1</v>
-      </c>
-      <c r="G29" s="15" t="s">
-        <v>315</v>
-      </c>
-      <c r="H29" s="36" t="s">
-        <v>316</v>
-      </c>
-      <c r="I29" s="17" t="s">
-        <v>218</v>
-      </c>
-      <c r="J29" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="K29" s="14">
-        <v>0</v>
-      </c>
-      <c r="L29" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3"/>
-      <c r="O29" s="3"/>
-      <c r="P29" s="3"/>
-      <c r="Q29" s="3"/>
-      <c r="R29" s="3"/>
-      <c r="S29" s="3"/>
-      <c r="T29" s="3"/>
-      <c r="U29" s="3"/>
-      <c r="V29" s="3"/>
-      <c r="W29" s="3"/>
-      <c r="X29" s="3"/>
+    <row r="36" spans="1:24">
+      <c r="A36" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E36" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F36" s="14">
+        <v>0</v>
+      </c>
+      <c r="G36" s="15" t="s">
+        <v>334</v>
+      </c>
+      <c r="H36" s="16"/>
+      <c r="I36" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="J36" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="K36" s="14">
+        <v>0</v>
+      </c>
+      <c r="L36" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3"/>
+      <c r="O36" s="3"/>
+      <c r="P36" s="3"/>
+      <c r="Q36" s="3"/>
+      <c r="R36" s="3"/>
+      <c r="S36" s="3"/>
+      <c r="T36" s="3"/>
+      <c r="U36" s="3"/>
+      <c r="V36" s="3"/>
+      <c r="W36" s="3"/>
+      <c r="X36" s="3"/>
     </row>
-    <row r="30" spans="1:24" ht="39">
-      <c r="A30" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="D30" s="9" t="s">
+    <row r="37" spans="1:24" ht="26">
+      <c r="A37" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="D37" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E30" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F30" s="9">
-        <v>0</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="H30" s="11" t="s">
-        <v>318</v>
-      </c>
-      <c r="I30" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="J30" s="9" t="s">
+      <c r="E37" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F37" s="9">
+        <v>0</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="H37" s="35" t="s">
+        <v>336</v>
+      </c>
+      <c r="I37" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="J37" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="K30" s="9">
-        <v>0</v>
-      </c>
-      <c r="L30" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M30" s="5"/>
-      <c r="N30" s="5"/>
-      <c r="O30" s="5"/>
-      <c r="P30" s="5"/>
-      <c r="Q30" s="5"/>
-      <c r="R30" s="5"/>
-      <c r="S30" s="5"/>
-      <c r="T30" s="5"/>
-      <c r="U30" s="5"/>
-      <c r="V30" s="5"/>
-      <c r="W30" s="5"/>
-      <c r="X30" s="5"/>
-    </row>
-    <row r="31" spans="1:24" ht="52">
-      <c r="A31" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="B31" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="E31" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F31" s="14">
-        <v>0</v>
-      </c>
-      <c r="G31" s="15" t="s">
-        <v>319</v>
-      </c>
-      <c r="H31" s="16" t="s">
-        <v>320</v>
-      </c>
-      <c r="I31" s="17" t="s">
-        <v>211</v>
-      </c>
-      <c r="J31" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="K31" s="14">
-        <v>0</v>
-      </c>
-      <c r="L31" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
-      <c r="O31" s="3"/>
-      <c r="P31" s="3"/>
-      <c r="Q31" s="3"/>
-      <c r="R31" s="3"/>
-      <c r="S31" s="3"/>
-      <c r="T31" s="3"/>
-      <c r="U31" s="3"/>
-      <c r="V31" s="3"/>
-      <c r="W31" s="3"/>
-      <c r="X31" s="3"/>
-    </row>
-    <row r="32" spans="1:24" ht="52">
-      <c r="A32" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E32" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F32" s="9">
-        <v>0</v>
-      </c>
-      <c r="G32" s="10" t="s">
-        <v>321</v>
-      </c>
-      <c r="H32" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="I32" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="J32" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="K32" s="9">
-        <v>0</v>
-      </c>
-      <c r="L32" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M32" s="5"/>
-      <c r="N32" s="5"/>
-      <c r="O32" s="5"/>
-      <c r="P32" s="5"/>
-      <c r="Q32" s="5"/>
-      <c r="R32" s="5"/>
-      <c r="S32" s="5"/>
-      <c r="T32" s="5"/>
-      <c r="U32" s="5"/>
-      <c r="V32" s="5"/>
-      <c r="W32" s="5"/>
-      <c r="X32" s="5"/>
-    </row>
-    <row r="33" spans="1:24" ht="78">
-      <c r="A33" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="E33" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F33" s="14">
-        <v>0</v>
-      </c>
-      <c r="G33" s="15" t="s">
-        <v>323</v>
-      </c>
-      <c r="H33" s="16" t="s">
-        <v>324</v>
-      </c>
-      <c r="I33" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="J33" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="K33" s="14">
-        <v>0</v>
-      </c>
-      <c r="L33" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M33" s="3"/>
-      <c r="N33" s="3"/>
-      <c r="O33" s="3"/>
-      <c r="P33" s="3"/>
-      <c r="Q33" s="3"/>
-      <c r="R33" s="3"/>
-      <c r="S33" s="3"/>
-      <c r="T33" s="3"/>
-      <c r="U33" s="3"/>
-      <c r="V33" s="3"/>
-      <c r="W33" s="3"/>
-      <c r="X33" s="3"/>
-    </row>
-    <row r="34" spans="1:24" ht="39">
-      <c r="A34" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E34" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F34" s="9">
-        <v>0</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="H34" s="11" t="s">
-        <v>326</v>
-      </c>
-      <c r="I34" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="J34" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="K34" s="9">
-        <v>0</v>
-      </c>
-      <c r="L34" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M34" s="5"/>
-      <c r="N34" s="5"/>
-      <c r="O34" s="5"/>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="5"/>
-      <c r="R34" s="5"/>
-      <c r="S34" s="5"/>
-      <c r="T34" s="5"/>
-      <c r="U34" s="5"/>
-      <c r="V34" s="5"/>
-      <c r="W34" s="5"/>
-      <c r="X34" s="5"/>
-    </row>
-    <row r="35" spans="1:24" ht="65.5" thickBot="1">
-      <c r="A35" s="37" t="s">
-        <v>201</v>
-      </c>
-      <c r="B35" s="37" t="s">
-        <v>201</v>
-      </c>
-      <c r="C35" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="D35" s="37" t="s">
-        <v>2</v>
-      </c>
-      <c r="E35" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="F35" s="37">
-        <v>0</v>
-      </c>
-      <c r="G35" s="38" t="s">
-        <v>327</v>
-      </c>
-      <c r="H35" s="39" t="s">
-        <v>287</v>
-      </c>
-      <c r="I35" s="40" t="s">
-        <v>199</v>
-      </c>
-      <c r="J35" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="K35" s="37">
-        <v>0</v>
-      </c>
-      <c r="L35" s="41" t="b">
-        <v>0</v>
-      </c>
-      <c r="M35" s="3"/>
-      <c r="N35" s="3"/>
-      <c r="O35" s="3"/>
-      <c r="P35" s="3"/>
-      <c r="Q35" s="3"/>
-      <c r="R35" s="3"/>
-      <c r="S35" s="3"/>
-      <c r="T35" s="3"/>
-      <c r="U35" s="3"/>
-      <c r="V35" s="3"/>
-      <c r="W35" s="3"/>
-      <c r="X35" s="3"/>
-    </row>
-    <row r="36" spans="1:24" ht="26.5" thickTop="1">
-      <c r="A36" s="31" t="s">
-        <v>328</v>
-      </c>
-      <c r="B36" s="31" t="s">
-        <v>328</v>
-      </c>
-      <c r="C36" s="31" t="s">
-        <v>198</v>
-      </c>
-      <c r="D36" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="E36" s="31" t="b">
-        <v>0</v>
-      </c>
-      <c r="F36" s="31">
-        <v>0</v>
-      </c>
-      <c r="G36" s="42" t="s">
-        <v>329</v>
-      </c>
-      <c r="H36" s="32" t="s">
-        <v>330</v>
-      </c>
-      <c r="I36" s="33" t="s">
-        <v>197</v>
-      </c>
-      <c r="J36" s="31" t="s">
-        <v>196</v>
-      </c>
-      <c r="K36" s="31">
-        <v>3</v>
-      </c>
-      <c r="L36" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="M36" s="5"/>
-      <c r="N36" s="5"/>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="5"/>
-      <c r="R36" s="5"/>
-      <c r="S36" s="5"/>
-      <c r="T36" s="5"/>
-      <c r="U36" s="5"/>
-      <c r="V36" s="5"/>
-      <c r="W36" s="5"/>
-      <c r="X36" s="5"/>
-    </row>
-    <row r="37" spans="1:24">
-      <c r="A37" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="D37" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="E37" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F37" s="14">
-        <v>0</v>
-      </c>
-      <c r="G37" s="15" t="s">
-        <v>331</v>
-      </c>
-      <c r="H37" s="16"/>
-      <c r="I37" s="17" t="s">
-        <v>193</v>
-      </c>
-      <c r="J37" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="K37" s="14">
-        <v>0</v>
-      </c>
-      <c r="L37" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M37" s="3"/>
-      <c r="N37" s="3"/>
-      <c r="O37" s="3"/>
-      <c r="P37" s="3"/>
-      <c r="Q37" s="3"/>
-      <c r="R37" s="3"/>
-      <c r="S37" s="3"/>
-      <c r="T37" s="3"/>
-      <c r="U37" s="3"/>
-      <c r="V37" s="3"/>
-      <c r="W37" s="3"/>
-      <c r="X37" s="3"/>
+      <c r="K37" s="9">
+        <v>0</v>
+      </c>
+      <c r="L37" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="5"/>
+      <c r="Q37" s="5"/>
+      <c r="R37" s="5"/>
+      <c r="S37" s="5"/>
+      <c r="T37" s="5"/>
+      <c r="U37" s="5"/>
+      <c r="V37" s="5"/>
+      <c r="W37" s="5"/>
+      <c r="X37" s="5"/>
     </row>
     <row r="38" spans="1:24" ht="26">
-      <c r="A38" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="D38" s="9" t="s">
+      <c r="A38" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="D38" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="E38" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F38" s="9">
-        <v>0</v>
-      </c>
-      <c r="G38" s="10" t="s">
-        <v>332</v>
-      </c>
-      <c r="H38" s="11" t="s">
-        <v>333</v>
-      </c>
-      <c r="I38" s="12" t="s">
-        <v>190</v>
-      </c>
-      <c r="J38" s="9" t="s">
+      <c r="E38" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="15" t="s">
+        <v>337</v>
+      </c>
+      <c r="H38" s="16"/>
+      <c r="I38" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="J38" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="K38" s="9">
-        <v>0</v>
-      </c>
-      <c r="L38" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M38" s="5"/>
-      <c r="N38" s="5"/>
-      <c r="O38" s="5"/>
-      <c r="P38" s="5"/>
-      <c r="Q38" s="5"/>
-      <c r="R38" s="5"/>
-      <c r="S38" s="5"/>
-      <c r="T38" s="5"/>
-      <c r="U38" s="5"/>
-      <c r="V38" s="5"/>
-      <c r="W38" s="5"/>
-      <c r="X38" s="5"/>
+      <c r="K38" s="14">
+        <v>0</v>
+      </c>
+      <c r="L38" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="3"/>
+      <c r="P38" s="3"/>
+      <c r="Q38" s="3"/>
+      <c r="R38" s="3"/>
+      <c r="S38" s="3"/>
+      <c r="T38" s="3"/>
+      <c r="U38" s="3"/>
+      <c r="V38" s="3"/>
+      <c r="W38" s="3"/>
+      <c r="X38" s="3"/>
     </row>
     <row r="39" spans="1:24">
-      <c r="A39" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="D39" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="E39" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F39" s="14">
-        <v>0</v>
-      </c>
-      <c r="G39" s="15" t="s">
-        <v>334</v>
-      </c>
-      <c r="H39" s="16"/>
-      <c r="I39" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="J39" s="14" t="s">
+      <c r="A39" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E39" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F39" s="9">
+        <v>0</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="H39" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="I39" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="J39" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="K39" s="14">
-        <v>0</v>
-      </c>
-      <c r="L39" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M39" s="3"/>
-      <c r="N39" s="3"/>
-      <c r="O39" s="3"/>
-      <c r="P39" s="3"/>
-      <c r="Q39" s="3"/>
-      <c r="R39" s="3"/>
-      <c r="S39" s="3"/>
-      <c r="T39" s="3"/>
-      <c r="U39" s="3"/>
-      <c r="V39" s="3"/>
-      <c r="W39" s="3"/>
-      <c r="X39" s="3"/>
+      <c r="K39" s="9">
+        <v>3</v>
+      </c>
+      <c r="L39" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
+      <c r="R39" s="5"/>
+      <c r="S39" s="5"/>
+      <c r="T39" s="5"/>
+      <c r="U39" s="5"/>
+      <c r="V39" s="5"/>
+      <c r="W39" s="5"/>
+      <c r="X39" s="5"/>
     </row>
     <row r="40" spans="1:24" ht="26">
-      <c r="A40" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="D40" s="9" t="s">
+      <c r="A40" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="D40" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E40" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F40" s="14">
+        <v>0</v>
+      </c>
+      <c r="G40" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="H40" s="16" t="s">
+        <v>341</v>
+      </c>
+      <c r="I40" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="J40" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="K40" s="14">
+        <v>0</v>
+      </c>
+      <c r="L40" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="1:24" ht="65">
+      <c r="A41" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="D41" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E40" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F40" s="9">
-        <v>0</v>
-      </c>
-      <c r="G40" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="H40" s="35" t="s">
-        <v>336</v>
-      </c>
-      <c r="I40" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="J40" s="9" t="s">
+      <c r="E41" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F41" s="9">
+        <v>0</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="H41" s="11"/>
+      <c r="I41" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="J41" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="K40" s="9">
-        <v>0</v>
-      </c>
-      <c r="L40" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M40" s="5"/>
-      <c r="N40" s="5"/>
-      <c r="O40" s="5"/>
-      <c r="P40" s="5"/>
-      <c r="Q40" s="5"/>
-      <c r="R40" s="5"/>
-      <c r="S40" s="5"/>
-      <c r="T40" s="5"/>
-      <c r="U40" s="5"/>
-      <c r="V40" s="5"/>
-      <c r="W40" s="5"/>
-      <c r="X40" s="5"/>
-    </row>
-    <row r="41" spans="1:24" ht="26">
-      <c r="A41" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="B41" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="C41" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="D41" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="E41" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F41" s="14">
-        <v>0</v>
-      </c>
-      <c r="G41" s="15" t="s">
-        <v>337</v>
-      </c>
-      <c r="H41" s="16"/>
-      <c r="I41" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="J41" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="K41" s="14">
-        <v>0</v>
-      </c>
-      <c r="L41" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M41" s="3"/>
-      <c r="N41" s="3"/>
-      <c r="O41" s="3"/>
-      <c r="P41" s="3"/>
-      <c r="Q41" s="3"/>
-      <c r="R41" s="3"/>
-      <c r="S41" s="3"/>
-      <c r="T41" s="3"/>
-      <c r="U41" s="3"/>
-      <c r="V41" s="3"/>
-      <c r="W41" s="3"/>
-      <c r="X41" s="3"/>
+      <c r="K41" s="9">
+        <v>0</v>
+      </c>
+      <c r="L41" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="5"/>
+      <c r="R41" s="5"/>
+      <c r="S41" s="5"/>
+      <c r="T41" s="5"/>
+      <c r="U41" s="5"/>
+      <c r="V41" s="5"/>
+      <c r="W41" s="5"/>
+      <c r="X41" s="5"/>
     </row>
     <row r="42" spans="1:24">
-      <c r="A42" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E42" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F42" s="9">
-        <v>0</v>
-      </c>
-      <c r="G42" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="H42" s="11" t="s">
-        <v>339</v>
-      </c>
-      <c r="I42" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="J42" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="K42" s="9">
-        <v>3</v>
-      </c>
-      <c r="L42" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M42" s="5"/>
-      <c r="N42" s="5"/>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="5"/>
-      <c r="R42" s="5"/>
-      <c r="S42" s="5"/>
-      <c r="T42" s="5"/>
-      <c r="U42" s="5"/>
-      <c r="V42" s="5"/>
-      <c r="W42" s="5"/>
-      <c r="X42" s="5"/>
+      <c r="A42" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="D42" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E42" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F42" s="14">
+        <v>0</v>
+      </c>
+      <c r="G42" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="H42" s="16"/>
+      <c r="I42" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="J42" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K42" s="14">
+        <v>0</v>
+      </c>
+      <c r="L42" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M42" s="3"/>
+      <c r="N42" s="3"/>
+      <c r="O42" s="3"/>
+      <c r="P42" s="3"/>
+      <c r="Q42" s="3"/>
+      <c r="R42" s="3"/>
+      <c r="S42" s="3"/>
+      <c r="T42" s="3"/>
+      <c r="U42" s="3"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3"/>
+      <c r="X42" s="3"/>
     </row>
     <row r="43" spans="1:24" ht="26">
-      <c r="A43" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="B43" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="C43" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="D43" s="14" t="s">
+      <c r="A43" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="D43" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E43" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F43" s="14">
-        <v>0</v>
-      </c>
-      <c r="G43" s="15" t="s">
-        <v>340</v>
-      </c>
-      <c r="H43" s="16" t="s">
-        <v>341</v>
-      </c>
-      <c r="I43" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="J43" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="K43" s="14">
-        <v>0</v>
-      </c>
-      <c r="L43" s="18" t="b">
+      <c r="E43" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F43" s="9">
+        <v>0</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="H43" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="I43" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="J43" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="K43" s="9">
+        <v>0</v>
+      </c>
+      <c r="L43" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="M43" s="3"/>
-      <c r="N43" s="3"/>
-      <c r="O43" s="3"/>
-      <c r="P43" s="3"/>
-      <c r="Q43" s="3"/>
-      <c r="R43" s="3"/>
-      <c r="S43" s="3"/>
-      <c r="T43" s="3"/>
-      <c r="U43" s="3"/>
-      <c r="V43" s="3"/>
-      <c r="W43" s="3"/>
-      <c r="X43" s="3"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="5"/>
+      <c r="P43" s="5"/>
+      <c r="Q43" s="5"/>
+      <c r="R43" s="5"/>
+      <c r="S43" s="5"/>
+      <c r="T43" s="5"/>
+      <c r="U43" s="5"/>
+      <c r="V43" s="5"/>
+      <c r="W43" s="5"/>
+      <c r="X43" s="5"/>
     </row>
-    <row r="44" spans="1:24" ht="65">
-      <c r="A44" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="B44" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="D44" s="9" t="s">
+    <row r="44" spans="1:24">
+      <c r="A44" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="D44" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="E44" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F44" s="9">
-        <v>0</v>
-      </c>
-      <c r="G44" s="10" t="s">
-        <v>342</v>
-      </c>
-      <c r="H44" s="11"/>
-      <c r="I44" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="J44" s="9" t="s">
+      <c r="E44" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F44" s="14">
+        <v>0</v>
+      </c>
+      <c r="G44" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="H44" s="16"/>
+      <c r="I44" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="J44" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K44" s="14">
+        <v>0</v>
+      </c>
+      <c r="L44" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M44" s="3"/>
+      <c r="N44" s="3"/>
+      <c r="O44" s="3"/>
+      <c r="P44" s="3"/>
+      <c r="Q44" s="3"/>
+      <c r="R44" s="3"/>
+      <c r="S44" s="3"/>
+      <c r="T44" s="3"/>
+      <c r="U44" s="3"/>
+      <c r="V44" s="3"/>
+      <c r="W44" s="3"/>
+      <c r="X44" s="3"/>
+    </row>
+    <row r="45" spans="1:24" ht="26">
+      <c r="A45" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E45" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F45" s="9">
+        <v>8</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="H45" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="I45" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="J45" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="K45" s="9">
+        <v>2</v>
+      </c>
+      <c r="L45" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="5"/>
+      <c r="P45" s="5"/>
+      <c r="Q45" s="5"/>
+      <c r="R45" s="5"/>
+      <c r="S45" s="5"/>
+      <c r="T45" s="5"/>
+      <c r="U45" s="5"/>
+      <c r="V45" s="5"/>
+      <c r="W45" s="5"/>
+      <c r="X45" s="5"/>
+    </row>
+    <row r="46" spans="1:24">
+      <c r="A46" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E46" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F46" s="14">
+        <v>0</v>
+      </c>
+      <c r="G46" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="H46" s="16" t="s">
+        <v>349</v>
+      </c>
+      <c r="I46" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="J46" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="9">
-        <v>0</v>
-      </c>
-      <c r="L44" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M44" s="5"/>
-      <c r="N44" s="5"/>
-      <c r="O44" s="5"/>
-      <c r="P44" s="5"/>
-      <c r="Q44" s="5"/>
-      <c r="R44" s="5"/>
-      <c r="S44" s="5"/>
-      <c r="T44" s="5"/>
-      <c r="U44" s="5"/>
-      <c r="V44" s="5"/>
-      <c r="W44" s="5"/>
-      <c r="X44" s="5"/>
-    </row>
-    <row r="45" spans="1:24">
-      <c r="A45" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="B45" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="C45" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="D45" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="E45" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F45" s="14">
-        <v>0</v>
-      </c>
-      <c r="G45" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="H45" s="16"/>
-      <c r="I45" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="J45" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="K45" s="14">
-        <v>0</v>
-      </c>
-      <c r="L45" s="18" t="b">
+      <c r="K46" s="14">
+        <v>0</v>
+      </c>
+      <c r="L46" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="M45" s="3"/>
-      <c r="N45" s="3"/>
-      <c r="O45" s="3"/>
-      <c r="P45" s="3"/>
-      <c r="Q45" s="3"/>
-      <c r="R45" s="3"/>
-      <c r="S45" s="3"/>
-      <c r="T45" s="3"/>
-      <c r="U45" s="3"/>
-      <c r="V45" s="3"/>
-      <c r="W45" s="3"/>
-      <c r="X45" s="3"/>
-    </row>
-    <row r="46" spans="1:24" ht="26">
-      <c r="A46" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="B46" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E46" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F46" s="9">
-        <v>0</v>
-      </c>
-      <c r="G46" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="H46" s="11" t="s">
-        <v>344</v>
-      </c>
-      <c r="I46" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="J46" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="K46" s="9">
-        <v>0</v>
-      </c>
-      <c r="L46" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M46" s="5"/>
-      <c r="N46" s="5"/>
-      <c r="O46" s="5"/>
-      <c r="P46" s="5"/>
-      <c r="Q46" s="5"/>
-      <c r="R46" s="5"/>
-      <c r="S46" s="5"/>
-      <c r="T46" s="5"/>
-      <c r="U46" s="5"/>
-      <c r="V46" s="5"/>
-      <c r="W46" s="5"/>
-      <c r="X46" s="5"/>
+      <c r="M46" s="3"/>
+      <c r="N46" s="3"/>
+      <c r="O46" s="3"/>
+      <c r="P46" s="3"/>
+      <c r="Q46" s="3"/>
+      <c r="R46" s="3"/>
+      <c r="S46" s="3"/>
+      <c r="T46" s="3"/>
+      <c r="U46" s="3"/>
+      <c r="V46" s="3"/>
+      <c r="W46" s="3"/>
+      <c r="X46" s="3"/>
     </row>
     <row r="47" spans="1:24">
-      <c r="A47" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="B47" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="C47" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="D47" s="14" t="s">
+      <c r="A47" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E47" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F47" s="9">
+        <v>0</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="H47" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="I47" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="J47" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="K47" s="9">
+        <v>0</v>
+      </c>
+      <c r="L47" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M47" s="5"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="5"/>
+      <c r="P47" s="5"/>
+      <c r="Q47" s="5"/>
+      <c r="R47" s="5"/>
+      <c r="S47" s="5"/>
+      <c r="T47" s="5"/>
+      <c r="U47" s="5"/>
+      <c r="V47" s="5"/>
+      <c r="W47" s="5"/>
+      <c r="X47" s="5"/>
+    </row>
+    <row r="48" spans="1:24">
+      <c r="A48" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="D48" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="E47" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F47" s="14">
-        <v>0</v>
-      </c>
-      <c r="G47" s="15" t="s">
-        <v>345</v>
-      </c>
-      <c r="H47" s="16"/>
-      <c r="I47" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="J47" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="K47" s="14">
-        <v>0</v>
-      </c>
-      <c r="L47" s="18" t="b">
+      <c r="E48" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F48" s="14">
+        <v>0</v>
+      </c>
+      <c r="G48" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="H48" s="16"/>
+      <c r="I48" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="J48" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="K48" s="14">
+        <v>0</v>
+      </c>
+      <c r="L48" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="M47" s="3"/>
-      <c r="N47" s="3"/>
-      <c r="O47" s="3"/>
-      <c r="P47" s="3"/>
-      <c r="Q47" s="3"/>
-      <c r="R47" s="3"/>
-      <c r="S47" s="3"/>
-      <c r="T47" s="3"/>
-      <c r="U47" s="3"/>
-      <c r="V47" s="3"/>
-      <c r="W47" s="3"/>
-      <c r="X47" s="3"/>
+      <c r="M48" s="3"/>
+      <c r="N48" s="3"/>
+      <c r="O48" s="3"/>
+      <c r="P48" s="3"/>
+      <c r="Q48" s="3"/>
+      <c r="R48" s="3"/>
+      <c r="S48" s="3"/>
+      <c r="T48" s="3"/>
+      <c r="U48" s="3"/>
+      <c r="V48" s="3"/>
+      <c r="W48" s="3"/>
+      <c r="X48" s="3"/>
     </row>
-    <row r="48" spans="1:24" ht="26">
-      <c r="A48" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="B48" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E48" s="9" t="b">
+    <row r="49" spans="1:24" ht="39">
+      <c r="A49" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E49" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F49" s="9">
+        <v>0</v>
+      </c>
+      <c r="G49" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="H49" s="11"/>
+      <c r="I49" s="12"/>
+      <c r="J49" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="K49" s="9">
+        <v>0</v>
+      </c>
+      <c r="L49" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M49" s="5"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="5"/>
+      <c r="P49" s="5"/>
+      <c r="Q49" s="5"/>
+      <c r="R49" s="5"/>
+      <c r="S49" s="5"/>
+      <c r="T49" s="5"/>
+      <c r="U49" s="5"/>
+      <c r="V49" s="5"/>
+      <c r="W49" s="5"/>
+      <c r="X49" s="5"/>
+    </row>
+    <row r="50" spans="1:24" ht="39">
+      <c r="A50" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="B50" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="D50" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E50" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F50" s="14">
+        <v>0</v>
+      </c>
+      <c r="G50" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="H50" s="16"/>
+      <c r="I50" s="17"/>
+      <c r="J50" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="K50" s="14">
+        <v>0</v>
+      </c>
+      <c r="L50" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3"/>
+      <c r="O50" s="3"/>
+      <c r="P50" s="3"/>
+      <c r="Q50" s="3"/>
+      <c r="R50" s="3"/>
+      <c r="S50" s="3"/>
+      <c r="T50" s="3"/>
+      <c r="U50" s="3"/>
+      <c r="V50" s="3"/>
+      <c r="W50" s="3"/>
+      <c r="X50" s="3"/>
+    </row>
+    <row r="51" spans="1:24" ht="26">
+      <c r="A51" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E51" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F51" s="9">
+        <v>0</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="H51" s="11"/>
+      <c r="I51" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="J51" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="K51" s="9">
+        <v>0</v>
+      </c>
+      <c r="L51" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="F48" s="9">
-        <v>8</v>
-      </c>
-      <c r="G48" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="H48" s="11" t="s">
-        <v>347</v>
-      </c>
-      <c r="I48" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="J48" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="K48" s="9">
+      <c r="M51" s="5"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="5"/>
+      <c r="P51" s="5"/>
+      <c r="Q51" s="5"/>
+      <c r="R51" s="5"/>
+      <c r="S51" s="5"/>
+      <c r="T51" s="5"/>
+      <c r="U51" s="5"/>
+      <c r="V51" s="5"/>
+      <c r="W51" s="5"/>
+      <c r="X51" s="5"/>
+    </row>
+    <row r="52" spans="1:24">
+      <c r="A52" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D52" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="L48" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M48" s="5"/>
-      <c r="N48" s="5"/>
-      <c r="O48" s="5"/>
-      <c r="P48" s="5"/>
-      <c r="Q48" s="5"/>
-      <c r="R48" s="5"/>
-      <c r="S48" s="5"/>
-      <c r="T48" s="5"/>
-      <c r="U48" s="5"/>
-      <c r="V48" s="5"/>
-      <c r="W48" s="5"/>
-      <c r="X48" s="5"/>
-    </row>
-    <row r="49" spans="1:24">
-      <c r="A49" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="B49" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="C49" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="D49" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="E49" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F49" s="14">
-        <v>0</v>
-      </c>
-      <c r="G49" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="H49" s="16" t="s">
-        <v>349</v>
-      </c>
-      <c r="I49" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="J49" s="14" t="s">
+      <c r="E52" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F52" s="14">
+        <v>0</v>
+      </c>
+      <c r="G52" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="H52" s="16"/>
+      <c r="I52" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="J52" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="K49" s="14">
-        <v>0</v>
-      </c>
-      <c r="L49" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M49" s="3"/>
-      <c r="N49" s="3"/>
-      <c r="O49" s="3"/>
-      <c r="P49" s="3"/>
-      <c r="Q49" s="3"/>
-      <c r="R49" s="3"/>
-      <c r="S49" s="3"/>
-      <c r="T49" s="3"/>
-      <c r="U49" s="3"/>
-      <c r="V49" s="3"/>
-      <c r="W49" s="3"/>
-      <c r="X49" s="3"/>
-    </row>
-    <row r="50" spans="1:24">
-      <c r="A50" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="C50" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E50" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F50" s="9">
-        <v>0</v>
-      </c>
-      <c r="G50" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="H50" s="11" t="s">
-        <v>351</v>
-      </c>
-      <c r="I50" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="J50" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="K50" s="9">
-        <v>0</v>
-      </c>
-      <c r="L50" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M50" s="5"/>
-      <c r="N50" s="5"/>
-      <c r="O50" s="5"/>
-      <c r="P50" s="5"/>
-      <c r="Q50" s="5"/>
-      <c r="R50" s="5"/>
-      <c r="S50" s="5"/>
-      <c r="T50" s="5"/>
-      <c r="U50" s="5"/>
-      <c r="V50" s="5"/>
-      <c r="W50" s="5"/>
-      <c r="X50" s="5"/>
-    </row>
-    <row r="51" spans="1:24">
-      <c r="A51" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="B51" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="C51" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="D51" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="E51" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F51" s="14">
-        <v>0</v>
-      </c>
-      <c r="G51" s="15" t="s">
-        <v>352</v>
-      </c>
-      <c r="H51" s="16"/>
-      <c r="I51" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="J51" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="K51" s="14">
-        <v>0</v>
-      </c>
-      <c r="L51" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M51" s="3"/>
-      <c r="N51" s="3"/>
-      <c r="O51" s="3"/>
-      <c r="P51" s="3"/>
-      <c r="Q51" s="3"/>
-      <c r="R51" s="3"/>
-      <c r="S51" s="3"/>
-      <c r="T51" s="3"/>
-      <c r="U51" s="3"/>
-      <c r="V51" s="3"/>
-      <c r="W51" s="3"/>
-      <c r="X51" s="3"/>
-    </row>
-    <row r="52" spans="1:24" ht="39">
-      <c r="A52" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E52" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F52" s="9">
-        <v>0</v>
-      </c>
-      <c r="G52" s="10" t="s">
-        <v>353</v>
-      </c>
-      <c r="H52" s="11"/>
-      <c r="I52" s="12"/>
-      <c r="J52" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="K52" s="9">
-        <v>0</v>
-      </c>
-      <c r="L52" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M52" s="5"/>
-      <c r="N52" s="5"/>
-      <c r="O52" s="5"/>
-      <c r="P52" s="5"/>
-      <c r="Q52" s="5"/>
-      <c r="R52" s="5"/>
-      <c r="S52" s="5"/>
-      <c r="T52" s="5"/>
-      <c r="U52" s="5"/>
-      <c r="V52" s="5"/>
-      <c r="W52" s="5"/>
-      <c r="X52" s="5"/>
+      <c r="K52" s="14">
+        <v>0</v>
+      </c>
+      <c r="L52" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3"/>
+      <c r="N52" s="3"/>
+      <c r="O52" s="3"/>
+      <c r="P52" s="3"/>
+      <c r="Q52" s="3"/>
+      <c r="R52" s="3"/>
+      <c r="S52" s="3"/>
+      <c r="T52" s="3"/>
+      <c r="U52" s="3"/>
+      <c r="V52" s="3"/>
+      <c r="W52" s="3"/>
+      <c r="X52" s="3"/>
     </row>
     <row r="53" spans="1:24" ht="39">
-      <c r="A53" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="B53" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="C53" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="D53" s="14" t="s">
+      <c r="A53" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="D53" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E53" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F53" s="14">
-        <v>0</v>
-      </c>
-      <c r="G53" s="15" t="s">
-        <v>354</v>
-      </c>
-      <c r="H53" s="16"/>
-      <c r="I53" s="17"/>
-      <c r="J53" s="14" t="s">
+      <c r="E53" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F53" s="9">
+        <v>0</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="H53" s="11"/>
+      <c r="I53" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="J53" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="K53" s="14">
-        <v>0</v>
-      </c>
-      <c r="L53" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M53" s="3"/>
-      <c r="N53" s="3"/>
-      <c r="O53" s="3"/>
-      <c r="P53" s="3"/>
-      <c r="Q53" s="3"/>
-      <c r="R53" s="3"/>
-      <c r="S53" s="3"/>
-      <c r="T53" s="3"/>
-      <c r="U53" s="3"/>
-      <c r="V53" s="3"/>
-      <c r="W53" s="3"/>
-      <c r="X53" s="3"/>
+      <c r="K53" s="9">
+        <v>0</v>
+      </c>
+      <c r="L53" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M53" s="5"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="5"/>
+      <c r="P53" s="5"/>
+      <c r="Q53" s="5"/>
+      <c r="R53" s="5"/>
+      <c r="S53" s="5"/>
+      <c r="T53" s="5"/>
+      <c r="U53" s="5"/>
+      <c r="V53" s="5"/>
+      <c r="W53" s="5"/>
+      <c r="X53" s="5"/>
     </row>
-    <row r="54" spans="1:24" ht="26">
-      <c r="A54" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C54" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="D54" s="9" t="s">
+    <row r="54" spans="1:24">
+      <c r="A54" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="B54" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="C54" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D54" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="E54" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F54" s="9">
-        <v>0</v>
-      </c>
-      <c r="G54" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="H54" s="11"/>
-      <c r="I54" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="J54" s="9" t="s">
+      <c r="E54" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="15" t="s">
+        <v>358</v>
+      </c>
+      <c r="H54" s="16"/>
+      <c r="I54" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="J54" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="K54" s="14">
+        <v>0</v>
+      </c>
+      <c r="L54" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M54" s="3"/>
+      <c r="N54" s="3"/>
+      <c r="O54" s="3"/>
+      <c r="P54" s="3"/>
+      <c r="Q54" s="3"/>
+      <c r="R54" s="3"/>
+      <c r="S54" s="3"/>
+      <c r="T54" s="3"/>
+      <c r="U54" s="3"/>
+      <c r="V54" s="3"/>
+      <c r="W54" s="3"/>
+      <c r="X54" s="3"/>
+    </row>
+    <row r="55" spans="1:24" ht="143">
+      <c r="A55" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E55" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F55" s="9">
+        <v>0</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="H55" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="I55" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="J55" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="K55" s="9">
+        <v>3</v>
+      </c>
+      <c r="L55" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M55" s="5"/>
+      <c r="N55" s="5"/>
+      <c r="O55" s="5"/>
+      <c r="P55" s="5"/>
+      <c r="Q55" s="5"/>
+      <c r="R55" s="5"/>
+      <c r="S55" s="5"/>
+      <c r="T55" s="5"/>
+      <c r="U55" s="5"/>
+      <c r="V55" s="5"/>
+      <c r="W55" s="5"/>
+      <c r="X55" s="5"/>
+    </row>
+    <row r="56" spans="1:24" ht="26">
+      <c r="A56" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="B56" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="C56" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="D56" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E56" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F56" s="14">
+        <v>0</v>
+      </c>
+      <c r="G56" s="15" t="s">
+        <v>361</v>
+      </c>
+      <c r="H56" s="16"/>
+      <c r="I56" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="J56" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="K54" s="9">
-        <v>0</v>
-      </c>
-      <c r="L54" s="13" t="b">
+      <c r="K56" s="14">
+        <v>0</v>
+      </c>
+      <c r="L56" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="M54" s="5"/>
-      <c r="N54" s="5"/>
-      <c r="O54" s="5"/>
-      <c r="P54" s="5"/>
-      <c r="Q54" s="5"/>
-      <c r="R54" s="5"/>
-      <c r="S54" s="5"/>
-      <c r="T54" s="5"/>
-      <c r="U54" s="5"/>
-      <c r="V54" s="5"/>
-      <c r="W54" s="5"/>
-      <c r="X54" s="5"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
     </row>
-    <row r="55" spans="1:24">
-      <c r="A55" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="B55" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="C55" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D55" s="14" t="s">
+    <row r="57" spans="1:24" ht="26">
+      <c r="A57" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="D57" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E55" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F55" s="14">
-        <v>0</v>
-      </c>
-      <c r="G55" s="15" t="s">
-        <v>356</v>
-      </c>
-      <c r="H55" s="16"/>
-      <c r="I55" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="J55" s="14" t="s">
+      <c r="E57" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F57" s="9">
+        <v>0</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="H57" s="11"/>
+      <c r="I57" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="J57" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="K55" s="14">
-        <v>0</v>
-      </c>
-      <c r="L55" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M55" s="3"/>
-      <c r="N55" s="3"/>
-      <c r="O55" s="3"/>
-      <c r="P55" s="3"/>
-      <c r="Q55" s="3"/>
-      <c r="R55" s="3"/>
-      <c r="S55" s="3"/>
-      <c r="T55" s="3"/>
-      <c r="U55" s="3"/>
-      <c r="V55" s="3"/>
-      <c r="W55" s="3"/>
-      <c r="X55" s="3"/>
+      <c r="K57" s="9">
+        <v>0</v>
+      </c>
+      <c r="L57" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M57" s="5"/>
+      <c r="N57" s="5"/>
+      <c r="O57" s="5"/>
+      <c r="P57" s="5"/>
+      <c r="Q57" s="5"/>
+      <c r="R57" s="5"/>
+      <c r="S57" s="5"/>
+      <c r="T57" s="5"/>
+      <c r="U57" s="5"/>
+      <c r="V57" s="5"/>
+      <c r="W57" s="5"/>
+      <c r="X57" s="5"/>
     </row>
-    <row r="56" spans="1:24" ht="39">
-      <c r="A56" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="B56" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="C56" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="D56" s="9" t="s">
+    <row r="58" spans="1:24" ht="26">
+      <c r="A58" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B58" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="C58" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="D58" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="E56" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F56" s="9">
-        <v>0</v>
-      </c>
-      <c r="G56" s="10" t="s">
-        <v>357</v>
-      </c>
-      <c r="H56" s="11"/>
-      <c r="I56" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="J56" s="9" t="s">
+      <c r="E58" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F58" s="14">
+        <v>0</v>
+      </c>
+      <c r="G58" s="15" t="s">
+        <v>363</v>
+      </c>
+      <c r="H58" s="16"/>
+      <c r="I58" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="J58" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="K56" s="9">
-        <v>0</v>
-      </c>
-      <c r="L56" s="13" t="b">
+      <c r="K58" s="14">
+        <v>0</v>
+      </c>
+      <c r="L58" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="M56" s="5"/>
-      <c r="N56" s="5"/>
-      <c r="O56" s="5"/>
-      <c r="P56" s="5"/>
-      <c r="Q56" s="5"/>
-      <c r="R56" s="5"/>
-      <c r="S56" s="5"/>
-      <c r="T56" s="5"/>
-      <c r="U56" s="5"/>
-      <c r="V56" s="5"/>
-      <c r="W56" s="5"/>
-      <c r="X56" s="5"/>
-    </row>
-    <row r="57" spans="1:24">
-      <c r="A57" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="B57" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="C57" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="D57" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="E57" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F57" s="14">
-        <v>0</v>
-      </c>
-      <c r="G57" s="15" t="s">
-        <v>358</v>
-      </c>
-      <c r="H57" s="16"/>
-      <c r="I57" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="J57" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="K57" s="14">
-        <v>0</v>
-      </c>
-      <c r="L57" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M57" s="3"/>
-      <c r="N57" s="3"/>
-      <c r="O57" s="3"/>
-      <c r="P57" s="3"/>
-      <c r="Q57" s="3"/>
-      <c r="R57" s="3"/>
-      <c r="S57" s="3"/>
-      <c r="T57" s="3"/>
-      <c r="U57" s="3"/>
-      <c r="V57" s="3"/>
-      <c r="W57" s="3"/>
-      <c r="X57" s="3"/>
-    </row>
-    <row r="58" spans="1:24" ht="143">
-      <c r="A58" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="B58" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="D58" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E58" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F58" s="9">
-        <v>0</v>
-      </c>
-      <c r="G58" s="10" t="s">
-        <v>359</v>
-      </c>
-      <c r="H58" s="11" t="s">
-        <v>360</v>
-      </c>
-      <c r="I58" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="J58" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="K58" s="9">
-        <v>3</v>
-      </c>
-      <c r="L58" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M58" s="5"/>
-      <c r="N58" s="5"/>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="5"/>
-      <c r="R58" s="5"/>
-      <c r="S58" s="5"/>
-      <c r="T58" s="5"/>
-      <c r="U58" s="5"/>
-      <c r="V58" s="5"/>
-      <c r="W58" s="5"/>
-      <c r="X58" s="5"/>
+      <c r="M58" s="3"/>
+      <c r="N58" s="3"/>
+      <c r="O58" s="3"/>
+      <c r="P58" s="3"/>
+      <c r="Q58" s="3"/>
+      <c r="R58" s="3"/>
+      <c r="S58" s="3"/>
+      <c r="T58" s="3"/>
+      <c r="U58" s="3"/>
+      <c r="V58" s="3"/>
+      <c r="W58" s="3"/>
+      <c r="X58" s="3"/>
     </row>
     <row r="59" spans="1:24" ht="26">
-      <c r="A59" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="B59" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="C59" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="D59" s="14" t="s">
+      <c r="A59" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="D59" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E59" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F59" s="14">
-        <v>0</v>
-      </c>
-      <c r="G59" s="15" t="s">
-        <v>361</v>
-      </c>
-      <c r="H59" s="16"/>
-      <c r="I59" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="J59" s="14" t="s">
+      <c r="E59" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F59" s="9">
+        <v>0</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="H59" s="11"/>
+      <c r="I59" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="J59" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="K59" s="14">
-        <v>0</v>
-      </c>
-      <c r="L59" s="18" t="b">
+      <c r="K59" s="9">
+        <v>0</v>
+      </c>
+      <c r="L59" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="M59" s="3"/>
-      <c r="N59" s="3"/>
-      <c r="O59" s="3"/>
-      <c r="P59" s="3"/>
-      <c r="Q59" s="3"/>
-      <c r="R59" s="3"/>
-      <c r="S59" s="3"/>
-      <c r="T59" s="3"/>
-      <c r="U59" s="3"/>
-      <c r="V59" s="3"/>
-      <c r="W59" s="3"/>
-      <c r="X59" s="3"/>
+      <c r="M59" s="5"/>
+      <c r="N59" s="5"/>
+      <c r="O59" s="5"/>
+      <c r="P59" s="5"/>
+      <c r="Q59" s="5"/>
+      <c r="R59" s="5"/>
+      <c r="S59" s="5"/>
+      <c r="T59" s="5"/>
+      <c r="U59" s="5"/>
+      <c r="V59" s="5"/>
+      <c r="W59" s="5"/>
+      <c r="X59" s="5"/>
     </row>
-    <row r="60" spans="1:24" ht="26">
-      <c r="A60" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="B60" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="C60" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="D60" s="9" t="s">
+    <row r="60" spans="1:24">
+      <c r="A60" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="B60" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C60" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="D60" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="E60" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F60" s="9">
-        <v>0</v>
-      </c>
-      <c r="G60" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="H60" s="11"/>
-      <c r="I60" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="J60" s="9" t="s">
+      <c r="E60" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F60" s="14">
+        <v>0</v>
+      </c>
+      <c r="G60" s="15" t="s">
+        <v>365</v>
+      </c>
+      <c r="H60" s="16"/>
+      <c r="I60" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="J60" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="K60" s="9">
-        <v>0</v>
-      </c>
-      <c r="L60" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M60" s="5"/>
-      <c r="N60" s="5"/>
-      <c r="O60" s="5"/>
-      <c r="P60" s="5"/>
-      <c r="Q60" s="5"/>
-      <c r="R60" s="5"/>
-      <c r="S60" s="5"/>
-      <c r="T60" s="5"/>
-      <c r="U60" s="5"/>
-      <c r="V60" s="5"/>
-      <c r="W60" s="5"/>
-      <c r="X60" s="5"/>
+      <c r="K60" s="14">
+        <v>0</v>
+      </c>
+      <c r="L60" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M60" s="3"/>
+      <c r="N60" s="3"/>
+      <c r="O60" s="3"/>
+      <c r="P60" s="3"/>
+      <c r="Q60" s="3"/>
+      <c r="R60" s="3"/>
+      <c r="S60" s="3"/>
+      <c r="T60" s="3"/>
+      <c r="U60" s="3"/>
+      <c r="V60" s="3"/>
+      <c r="W60" s="3"/>
+      <c r="X60" s="3"/>
     </row>
-    <row r="61" spans="1:24" ht="26">
-      <c r="A61" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="B61" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="C61" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="D61" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="E61" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F61" s="14">
-        <v>0</v>
-      </c>
-      <c r="G61" s="15" t="s">
-        <v>363</v>
-      </c>
-      <c r="H61" s="16"/>
-      <c r="I61" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="J61" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="K61" s="14">
-        <v>0</v>
-      </c>
-      <c r="L61" s="18" t="b">
+    <row r="61" spans="1:24">
+      <c r="A61" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E61" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="M61" s="3"/>
-      <c r="N61" s="3"/>
-      <c r="O61" s="3"/>
-      <c r="P61" s="3"/>
-      <c r="Q61" s="3"/>
-      <c r="R61" s="3"/>
-      <c r="S61" s="3"/>
-      <c r="T61" s="3"/>
-      <c r="U61" s="3"/>
-      <c r="V61" s="3"/>
-      <c r="W61" s="3"/>
-      <c r="X61" s="3"/>
+      <c r="F61" s="9">
+        <v>1</v>
+      </c>
+      <c r="G61" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="H61" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="I61" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="J61" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="K61" s="9">
+        <v>0</v>
+      </c>
+      <c r="L61" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M61" s="5"/>
+      <c r="N61" s="5"/>
+      <c r="O61" s="5"/>
+      <c r="P61" s="5"/>
+      <c r="Q61" s="5"/>
+      <c r="R61" s="5"/>
+      <c r="S61" s="5"/>
+      <c r="T61" s="5"/>
+      <c r="U61" s="5"/>
+      <c r="V61" s="5"/>
+      <c r="W61" s="5"/>
+      <c r="X61" s="5"/>
     </row>
     <row r="62" spans="1:24" ht="26">
-      <c r="A62" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="B62" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="D62" s="9" t="s">
+      <c r="A62" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="B62" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C62" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D62" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="E62" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F62" s="9">
-        <v>0</v>
-      </c>
-      <c r="G62" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="H62" s="11"/>
-      <c r="I62" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="J62" s="9" t="s">
+      <c r="E62" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F62" s="14">
+        <v>1</v>
+      </c>
+      <c r="G62" s="15" t="s">
+        <v>368</v>
+      </c>
+      <c r="H62" s="16"/>
+      <c r="I62" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="J62" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="K62" s="9">
-        <v>0</v>
-      </c>
-      <c r="L62" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M62" s="5"/>
-      <c r="N62" s="5"/>
-      <c r="O62" s="5"/>
-      <c r="P62" s="5"/>
-      <c r="Q62" s="5"/>
-      <c r="R62" s="5"/>
-      <c r="S62" s="5"/>
-      <c r="T62" s="5"/>
-      <c r="U62" s="5"/>
-      <c r="V62" s="5"/>
-      <c r="W62" s="5"/>
-      <c r="X62" s="5"/>
+      <c r="K62" s="14">
+        <v>0</v>
+      </c>
+      <c r="L62" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3"/>
+      <c r="N62" s="3"/>
+      <c r="O62" s="3"/>
+      <c r="P62" s="3"/>
+      <c r="Q62" s="3"/>
+      <c r="R62" s="3"/>
+      <c r="S62" s="3"/>
+      <c r="T62" s="3"/>
+      <c r="U62" s="3"/>
+      <c r="V62" s="3"/>
+      <c r="W62" s="3"/>
+      <c r="X62" s="3"/>
     </row>
     <row r="63" spans="1:24">
-      <c r="A63" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="B63" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C63" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="D63" s="14" t="s">
+      <c r="A63" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D63" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E63" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F63" s="14">
-        <v>0</v>
-      </c>
-      <c r="G63" s="15" t="s">
-        <v>365</v>
-      </c>
-      <c r="H63" s="16"/>
-      <c r="I63" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="J63" s="14" t="s">
+      <c r="E63" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F63" s="9">
+        <v>0</v>
+      </c>
+      <c r="G63" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="H63" s="11"/>
+      <c r="I63" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J63" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="K63" s="14">
-        <v>0</v>
-      </c>
-      <c r="L63" s="18" t="b">
+      <c r="K63" s="9">
+        <v>0</v>
+      </c>
+      <c r="L63" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M63" s="5"/>
+      <c r="N63" s="5"/>
+      <c r="O63" s="5"/>
+      <c r="P63" s="5"/>
+      <c r="Q63" s="5"/>
+      <c r="R63" s="5"/>
+      <c r="S63" s="5"/>
+      <c r="T63" s="5"/>
+      <c r="U63" s="5"/>
+      <c r="V63" s="5"/>
+      <c r="W63" s="5"/>
+      <c r="X63" s="5"/>
+    </row>
+    <row r="64" spans="1:24" ht="39">
+      <c r="A64" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="B64" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C64" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="D64" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E64" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="M63" s="3"/>
-      <c r="N63" s="3"/>
-      <c r="O63" s="3"/>
-      <c r="P63" s="3"/>
-      <c r="Q63" s="3"/>
-      <c r="R63" s="3"/>
-      <c r="S63" s="3"/>
-      <c r="T63" s="3"/>
-      <c r="U63" s="3"/>
-      <c r="V63" s="3"/>
-      <c r="W63" s="3"/>
-      <c r="X63" s="3"/>
-    </row>
-    <row r="64" spans="1:24">
-      <c r="A64" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="B64" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C64" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D64" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E64" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="F64" s="9">
-        <v>1</v>
-      </c>
-      <c r="G64" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="H64" s="11" t="s">
-        <v>367</v>
-      </c>
-      <c r="I64" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="J64" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="K64" s="9">
-        <v>0</v>
-      </c>
-      <c r="L64" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M64" s="5"/>
-      <c r="N64" s="5"/>
-      <c r="O64" s="5"/>
-      <c r="P64" s="5"/>
-      <c r="Q64" s="5"/>
-      <c r="R64" s="5"/>
-      <c r="S64" s="5"/>
-      <c r="T64" s="5"/>
-      <c r="U64" s="5"/>
-      <c r="V64" s="5"/>
-      <c r="W64" s="5"/>
-      <c r="X64" s="5"/>
+      <c r="F64" s="14">
+        <v>4</v>
+      </c>
+      <c r="G64" s="15" t="s">
+        <v>370</v>
+      </c>
+      <c r="H64" s="16"/>
+      <c r="I64" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="J64" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="K64" s="14">
+        <v>0</v>
+      </c>
+      <c r="L64" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+      <c r="N64" s="3"/>
+      <c r="O64" s="3"/>
+      <c r="P64" s="3"/>
+      <c r="Q64" s="3"/>
+      <c r="R64" s="3"/>
+      <c r="S64" s="3"/>
+      <c r="T64" s="3"/>
+      <c r="U64" s="3"/>
+      <c r="V64" s="3"/>
+      <c r="W64" s="3"/>
+      <c r="X64" s="3"/>
     </row>
     <row r="65" spans="1:24" ht="26">
-      <c r="A65" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="B65" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="C65" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="D65" s="14" t="s">
+      <c r="A65" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="D65" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E65" s="14" t="b">
+      <c r="E65" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F65" s="9">
+        <v>0</v>
+      </c>
+      <c r="G65" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="H65" s="11"/>
+      <c r="I65" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="J65" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="K65" s="9">
+        <v>0</v>
+      </c>
+      <c r="L65" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M65" s="5"/>
+      <c r="N65" s="5"/>
+      <c r="O65" s="5"/>
+      <c r="P65" s="5"/>
+      <c r="Q65" s="5"/>
+      <c r="R65" s="5"/>
+      <c r="S65" s="5"/>
+      <c r="T65" s="5"/>
+      <c r="U65" s="5"/>
+      <c r="V65" s="5"/>
+      <c r="W65" s="5"/>
+      <c r="X65" s="5"/>
+    </row>
+    <row r="66" spans="1:24" ht="26">
+      <c r="A66" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="B66" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C66" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D66" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E66" s="14" t="b">
         <v>1</v>
       </c>
-      <c r="F65" s="14">
+      <c r="F66" s="14">
         <v>1</v>
       </c>
-      <c r="G65" s="15" t="s">
-        <v>368</v>
-      </c>
-      <c r="H65" s="16"/>
-      <c r="I65" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="J65" s="14" t="s">
+      <c r="G66" s="15" t="s">
+        <v>372</v>
+      </c>
+      <c r="H66" s="16" t="s">
+        <v>351</v>
+      </c>
+      <c r="I66" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="J66" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="K66" s="14">
+        <v>0</v>
+      </c>
+      <c r="L66" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M66" s="3"/>
+      <c r="N66" s="3"/>
+      <c r="O66" s="3"/>
+      <c r="P66" s="3"/>
+      <c r="Q66" s="3"/>
+      <c r="R66" s="3"/>
+      <c r="S66" s="3"/>
+      <c r="T66" s="3"/>
+      <c r="U66" s="3"/>
+      <c r="V66" s="3"/>
+      <c r="W66" s="3"/>
+      <c r="X66" s="3"/>
+    </row>
+    <row r="67" spans="1:24">
+      <c r="A67" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E67" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F67" s="9">
+        <v>0</v>
+      </c>
+      <c r="G67" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="H67" s="11"/>
+      <c r="I67" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="J67" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="K65" s="14">
-        <v>0</v>
-      </c>
-      <c r="L65" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M65" s="3"/>
-      <c r="N65" s="3"/>
-      <c r="O65" s="3"/>
-      <c r="P65" s="3"/>
-      <c r="Q65" s="3"/>
-      <c r="R65" s="3"/>
-      <c r="S65" s="3"/>
-      <c r="T65" s="3"/>
-      <c r="U65" s="3"/>
-      <c r="V65" s="3"/>
-      <c r="W65" s="3"/>
-      <c r="X65" s="3"/>
+      <c r="K67" s="9">
+        <v>0</v>
+      </c>
+      <c r="L67" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M67" s="5"/>
+      <c r="N67" s="5"/>
+      <c r="O67" s="5"/>
+      <c r="P67" s="5"/>
+      <c r="Q67" s="5"/>
+      <c r="R67" s="5"/>
+      <c r="S67" s="5"/>
+      <c r="T67" s="5"/>
+      <c r="U67" s="5"/>
+      <c r="V67" s="5"/>
+      <c r="W67" s="5"/>
+      <c r="X67" s="5"/>
     </row>
-    <row r="66" spans="1:24">
-      <c r="A66" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="B66" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="C66" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="D66" s="9" t="s">
+    <row r="68" spans="1:24">
+      <c r="A68" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B68" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="C68" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="D68" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="E66" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F66" s="9">
-        <v>0</v>
-      </c>
-      <c r="G66" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="H66" s="11"/>
-      <c r="I66" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="J66" s="9" t="s">
+      <c r="E68" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F68" s="14">
+        <v>0</v>
+      </c>
+      <c r="G68" s="15" t="s">
+        <v>374</v>
+      </c>
+      <c r="H68" s="16"/>
+      <c r="I68" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="J68" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="K66" s="9">
-        <v>0</v>
-      </c>
-      <c r="L66" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M66" s="5"/>
-      <c r="N66" s="5"/>
-      <c r="O66" s="5"/>
-      <c r="P66" s="5"/>
-      <c r="Q66" s="5"/>
-      <c r="R66" s="5"/>
-      <c r="S66" s="5"/>
-      <c r="T66" s="5"/>
-      <c r="U66" s="5"/>
-      <c r="V66" s="5"/>
-      <c r="W66" s="5"/>
-      <c r="X66" s="5"/>
+      <c r="K68" s="14">
+        <v>0</v>
+      </c>
+      <c r="L68" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M68" s="3"/>
+      <c r="N68" s="3"/>
+      <c r="O68" s="3"/>
+      <c r="P68" s="3"/>
+      <c r="Q68" s="3"/>
+      <c r="R68" s="3"/>
+      <c r="S68" s="3"/>
+      <c r="T68" s="3"/>
+      <c r="U68" s="3"/>
+      <c r="V68" s="3"/>
+      <c r="W68" s="3"/>
+      <c r="X68" s="3"/>
     </row>
-    <row r="67" spans="1:24" ht="39">
-      <c r="A67" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="B67" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C67" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="D67" s="14" t="s">
+    <row r="69" spans="1:24">
+      <c r="A69" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D69" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E67" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="F67" s="14">
-        <v>4</v>
-      </c>
-      <c r="G67" s="15" t="s">
-        <v>370</v>
-      </c>
-      <c r="H67" s="16"/>
-      <c r="I67" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="J67" s="14" t="s">
+      <c r="E69" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F69" s="9">
+        <v>0</v>
+      </c>
+      <c r="G69" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="H69" s="11"/>
+      <c r="I69" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="J69" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="K67" s="14">
-        <v>0</v>
-      </c>
-      <c r="L67" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M67" s="3"/>
-      <c r="N67" s="3"/>
-      <c r="O67" s="3"/>
-      <c r="P67" s="3"/>
-      <c r="Q67" s="3"/>
-      <c r="R67" s="3"/>
-      <c r="S67" s="3"/>
-      <c r="T67" s="3"/>
-      <c r="U67" s="3"/>
-      <c r="V67" s="3"/>
-      <c r="W67" s="3"/>
-      <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="1:24" ht="26">
-      <c r="A68" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="B68" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="C68" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D68" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E68" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F68" s="9">
-        <v>0</v>
-      </c>
-      <c r="G68" s="10" t="s">
-        <v>371</v>
-      </c>
-      <c r="H68" s="11"/>
-      <c r="I68" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="J68" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="K68" s="9">
-        <v>0</v>
-      </c>
-      <c r="L68" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M68" s="5"/>
-      <c r="N68" s="5"/>
-      <c r="O68" s="5"/>
-      <c r="P68" s="5"/>
-      <c r="Q68" s="5"/>
-      <c r="R68" s="5"/>
-      <c r="S68" s="5"/>
-      <c r="T68" s="5"/>
-      <c r="U68" s="5"/>
-      <c r="V68" s="5"/>
-      <c r="W68" s="5"/>
-      <c r="X68" s="5"/>
-    </row>
-    <row r="69" spans="1:24" ht="26">
-      <c r="A69" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="B69" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="C69" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D69" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="E69" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="F69" s="14">
-        <v>1</v>
-      </c>
-      <c r="G69" s="15" t="s">
-        <v>372</v>
-      </c>
-      <c r="H69" s="16" t="s">
-        <v>351</v>
-      </c>
-      <c r="I69" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="J69" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="K69" s="14">
-        <v>0</v>
-      </c>
-      <c r="L69" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M69" s="3"/>
-      <c r="N69" s="3"/>
-      <c r="O69" s="3"/>
-      <c r="P69" s="3"/>
-      <c r="Q69" s="3"/>
-      <c r="R69" s="3"/>
-      <c r="S69" s="3"/>
-      <c r="T69" s="3"/>
-      <c r="U69" s="3"/>
-      <c r="V69" s="3"/>
-      <c r="W69" s="3"/>
-      <c r="X69" s="3"/>
+      <c r="K69" s="9">
+        <v>0</v>
+      </c>
+      <c r="L69" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M69" s="5"/>
+      <c r="N69" s="5"/>
+      <c r="O69" s="5"/>
+      <c r="P69" s="5"/>
+      <c r="Q69" s="5"/>
+      <c r="R69" s="5"/>
+      <c r="S69" s="5"/>
+      <c r="T69" s="5"/>
+      <c r="U69" s="5"/>
+      <c r="V69" s="5"/>
+      <c r="W69" s="5"/>
+      <c r="X69" s="5"/>
     </row>
     <row r="70" spans="1:24">
-      <c r="A70" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B70" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="C70" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="D70" s="9" t="s">
+      <c r="A70" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B70" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C70" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D70" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="E70" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F70" s="9">
-        <v>0</v>
-      </c>
-      <c r="G70" s="10" t="s">
-        <v>373</v>
-      </c>
-      <c r="H70" s="11"/>
-      <c r="I70" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="J70" s="9" t="s">
+      <c r="E70" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F70" s="14">
+        <v>0</v>
+      </c>
+      <c r="G70" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="H70" s="16"/>
+      <c r="I70" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="J70" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="K70" s="9">
-        <v>0</v>
-      </c>
-      <c r="L70" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M70" s="5"/>
-      <c r="N70" s="5"/>
-      <c r="O70" s="5"/>
-      <c r="P70" s="5"/>
-      <c r="Q70" s="5"/>
-      <c r="R70" s="5"/>
-      <c r="S70" s="5"/>
-      <c r="T70" s="5"/>
-      <c r="U70" s="5"/>
-      <c r="V70" s="5"/>
-      <c r="W70" s="5"/>
-      <c r="X70" s="5"/>
+      <c r="K70" s="14">
+        <v>0</v>
+      </c>
+      <c r="L70" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+      <c r="N70" s="3"/>
+      <c r="O70" s="3"/>
+      <c r="P70" s="3"/>
+      <c r="Q70" s="3"/>
+      <c r="R70" s="3"/>
+      <c r="S70" s="3"/>
+      <c r="T70" s="3"/>
+      <c r="U70" s="3"/>
+      <c r="V70" s="3"/>
+      <c r="W70" s="3"/>
+      <c r="X70" s="3"/>
     </row>
-    <row r="71" spans="1:24">
-      <c r="A71" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="B71" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="C71" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="D71" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="E71" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F71" s="14">
-        <v>0</v>
-      </c>
-      <c r="G71" s="15" t="s">
-        <v>374</v>
-      </c>
-      <c r="H71" s="16"/>
-      <c r="I71" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="J71" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="K71" s="14">
-        <v>0</v>
-      </c>
-      <c r="L71" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M71" s="3"/>
-      <c r="N71" s="3"/>
-      <c r="O71" s="3"/>
-      <c r="P71" s="3"/>
-      <c r="Q71" s="3"/>
-      <c r="R71" s="3"/>
-      <c r="S71" s="3"/>
-      <c r="T71" s="3"/>
-      <c r="U71" s="3"/>
-      <c r="V71" s="3"/>
-      <c r="W71" s="3"/>
-      <c r="X71" s="3"/>
+    <row r="71" spans="1:24" ht="26">
+      <c r="A71" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E71" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F71" s="9">
+        <v>0</v>
+      </c>
+      <c r="G71" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="H71" s="11" t="s">
+        <v>378</v>
+      </c>
+      <c r="I71" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="J71" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K71" s="9">
+        <v>8</v>
+      </c>
+      <c r="L71" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M71" s="5"/>
+      <c r="N71" s="5"/>
+      <c r="O71" s="5"/>
+      <c r="P71" s="5"/>
+      <c r="Q71" s="5"/>
+      <c r="R71" s="5"/>
+      <c r="S71" s="5"/>
+      <c r="T71" s="5"/>
+      <c r="U71" s="5"/>
+      <c r="V71" s="5"/>
+      <c r="W71" s="5"/>
+      <c r="X71" s="5"/>
     </row>
     <row r="72" spans="1:24">
-      <c r="A72" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="B72" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="C72" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D72" s="9" t="s">
+      <c r="A72" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B72" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C72" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D72" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="E72" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F72" s="9">
-        <v>0</v>
-      </c>
-      <c r="G72" s="10" t="s">
-        <v>375</v>
-      </c>
-      <c r="H72" s="11"/>
-      <c r="I72" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="J72" s="9" t="s">
+      <c r="E72" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F72" s="14">
+        <v>0</v>
+      </c>
+      <c r="G72" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="H72" s="16"/>
+      <c r="I72" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="J72" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="K72" s="9">
-        <v>0</v>
-      </c>
-      <c r="L72" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M72" s="5"/>
-      <c r="N72" s="5"/>
-      <c r="O72" s="5"/>
-      <c r="P72" s="5"/>
-      <c r="Q72" s="5"/>
-      <c r="R72" s="5"/>
-      <c r="S72" s="5"/>
-      <c r="T72" s="5"/>
-      <c r="U72" s="5"/>
-      <c r="V72" s="5"/>
-      <c r="W72" s="5"/>
-      <c r="X72" s="5"/>
+      <c r="K72" s="14">
+        <v>0</v>
+      </c>
+      <c r="L72" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M72" s="3"/>
+      <c r="N72" s="3"/>
+      <c r="O72" s="3"/>
+      <c r="P72" s="3"/>
+      <c r="Q72" s="3"/>
+      <c r="R72" s="3"/>
+      <c r="S72" s="3"/>
+      <c r="T72" s="3"/>
+      <c r="U72" s="3"/>
+      <c r="V72" s="3"/>
+      <c r="W72" s="3"/>
+      <c r="X72" s="3"/>
     </row>
-    <row r="73" spans="1:24">
-      <c r="A73" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="B73" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="C73" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="D73" s="14" t="s">
+    <row r="73" spans="1:24" ht="39">
+      <c r="A73" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D73" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E73" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F73" s="14">
-        <v>0</v>
-      </c>
-      <c r="G73" s="15" t="s">
-        <v>376</v>
-      </c>
-      <c r="H73" s="16"/>
-      <c r="I73" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="J73" s="14" t="s">
+      <c r="E73" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F73" s="9">
+        <v>1</v>
+      </c>
+      <c r="G73" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="H73" s="11"/>
+      <c r="I73" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="J73" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="K73" s="14">
-        <v>0</v>
-      </c>
-      <c r="L73" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M73" s="3"/>
-      <c r="N73" s="3"/>
-      <c r="O73" s="3"/>
-      <c r="P73" s="3"/>
-      <c r="Q73" s="3"/>
-      <c r="R73" s="3"/>
-      <c r="S73" s="3"/>
-      <c r="T73" s="3"/>
-      <c r="U73" s="3"/>
-      <c r="V73" s="3"/>
-      <c r="W73" s="3"/>
-      <c r="X73" s="3"/>
+      <c r="K73" s="9">
+        <v>0</v>
+      </c>
+      <c r="L73" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M73" s="5"/>
+      <c r="N73" s="5"/>
+      <c r="O73" s="5"/>
+      <c r="P73" s="5"/>
+      <c r="Q73" s="5"/>
+      <c r="R73" s="5"/>
+      <c r="S73" s="5"/>
+      <c r="T73" s="5"/>
+      <c r="U73" s="5"/>
+      <c r="V73" s="5"/>
+      <c r="W73" s="5"/>
+      <c r="X73" s="5"/>
     </row>
-    <row r="74" spans="1:24" ht="26">
-      <c r="A74" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="B74" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C74" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D74" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E74" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F74" s="9">
-        <v>0</v>
-      </c>
-      <c r="G74" s="10" t="s">
-        <v>377</v>
-      </c>
-      <c r="H74" s="11" t="s">
-        <v>378</v>
-      </c>
-      <c r="I74" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="J74" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="K74" s="9">
-        <v>8</v>
-      </c>
-      <c r="L74" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M74" s="5"/>
-      <c r="N74" s="5"/>
-      <c r="O74" s="5"/>
-      <c r="P74" s="5"/>
-      <c r="Q74" s="5"/>
-      <c r="R74" s="5"/>
-      <c r="S74" s="5"/>
-      <c r="T74" s="5"/>
-      <c r="U74" s="5"/>
-      <c r="V74" s="5"/>
-      <c r="W74" s="5"/>
-      <c r="X74" s="5"/>
+    <row r="74" spans="1:24" ht="52">
+      <c r="A74" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="B74" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C74" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="D74" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E74" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F74" s="14">
+        <v>0</v>
+      </c>
+      <c r="G74" s="15" t="s">
+        <v>381</v>
+      </c>
+      <c r="H74" s="16"/>
+      <c r="I74" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="J74" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="K74" s="14">
+        <v>0</v>
+      </c>
+      <c r="L74" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+      <c r="N74" s="3"/>
+      <c r="O74" s="3"/>
+      <c r="P74" s="3"/>
+      <c r="Q74" s="3"/>
+      <c r="R74" s="3"/>
+      <c r="S74" s="3"/>
+      <c r="T74" s="3"/>
+      <c r="U74" s="3"/>
+      <c r="V74" s="3"/>
+      <c r="W74" s="3"/>
+      <c r="X74" s="3"/>
     </row>
     <row r="75" spans="1:24">
-      <c r="A75" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="B75" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C75" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D75" s="14" t="s">
+      <c r="A75" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D75" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E75" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F75" s="14">
-        <v>0</v>
-      </c>
-      <c r="G75" s="15" t="s">
-        <v>379</v>
-      </c>
-      <c r="H75" s="16"/>
-      <c r="I75" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="J75" s="14" t="s">
+      <c r="E75" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F75" s="9">
+        <v>1</v>
+      </c>
+      <c r="G75" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="H75" s="11"/>
+      <c r="I75" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="J75" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="K75" s="14">
-        <v>0</v>
-      </c>
-      <c r="L75" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M75" s="3"/>
-      <c r="N75" s="3"/>
-      <c r="O75" s="3"/>
-      <c r="P75" s="3"/>
-      <c r="Q75" s="3"/>
-      <c r="R75" s="3"/>
-      <c r="S75" s="3"/>
-      <c r="T75" s="3"/>
-      <c r="U75" s="3"/>
-      <c r="V75" s="3"/>
-      <c r="W75" s="3"/>
-      <c r="X75" s="3"/>
+      <c r="K75" s="9">
+        <v>0</v>
+      </c>
+      <c r="L75" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M75" s="5"/>
+      <c r="N75" s="5"/>
+      <c r="O75" s="5"/>
+      <c r="P75" s="5"/>
+      <c r="Q75" s="5"/>
+      <c r="R75" s="5"/>
+      <c r="S75" s="5"/>
+      <c r="T75" s="5"/>
+      <c r="U75" s="5"/>
+      <c r="V75" s="5"/>
+      <c r="W75" s="5"/>
+      <c r="X75" s="5"/>
     </row>
-    <row r="76" spans="1:24" ht="39">
-      <c r="A76" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="B76" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C76" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D76" s="9" t="s">
+    <row r="76" spans="1:24" ht="26">
+      <c r="A76" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B76" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C76" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D76" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="E76" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="F76" s="9">
-        <v>1</v>
-      </c>
-      <c r="G76" s="10" t="s">
-        <v>380</v>
-      </c>
-      <c r="H76" s="11"/>
-      <c r="I76" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="J76" s="9" t="s">
+      <c r="E76" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F76" s="14">
+        <v>0</v>
+      </c>
+      <c r="G76" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="H76" s="16"/>
+      <c r="I76" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="J76" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="K76" s="9">
-        <v>0</v>
-      </c>
-      <c r="L76" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M76" s="5"/>
-      <c r="N76" s="5"/>
-      <c r="O76" s="5"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="5"/>
-      <c r="R76" s="5"/>
-      <c r="S76" s="5"/>
-      <c r="T76" s="5"/>
-      <c r="U76" s="5"/>
-      <c r="V76" s="5"/>
-      <c r="W76" s="5"/>
-      <c r="X76" s="5"/>
+      <c r="K76" s="14">
+        <v>0</v>
+      </c>
+      <c r="L76" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M76" s="3"/>
+      <c r="N76" s="3"/>
+      <c r="O76" s="3"/>
+      <c r="P76" s="3"/>
+      <c r="Q76" s="3"/>
+      <c r="R76" s="3"/>
+      <c r="S76" s="3"/>
+      <c r="T76" s="3"/>
+      <c r="U76" s="3"/>
+      <c r="V76" s="3"/>
+      <c r="W76" s="3"/>
+      <c r="X76" s="3"/>
     </row>
-    <row r="77" spans="1:24" ht="52">
-      <c r="A77" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="B77" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C77" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="D77" s="14" t="s">
+    <row r="77" spans="1:24" ht="26">
+      <c r="A77" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D77" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E77" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F77" s="14">
-        <v>0</v>
-      </c>
-      <c r="G77" s="15" t="s">
-        <v>381</v>
-      </c>
-      <c r="H77" s="16"/>
-      <c r="I77" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="J77" s="14" t="s">
+      <c r="E77" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F77" s="9">
+        <v>0</v>
+      </c>
+      <c r="G77" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="H77" s="11"/>
+      <c r="I77" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="J77" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="K77" s="14">
-        <v>0</v>
-      </c>
-      <c r="L77" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M77" s="3"/>
-      <c r="N77" s="3"/>
-      <c r="O77" s="3"/>
-      <c r="P77" s="3"/>
-      <c r="Q77" s="3"/>
-      <c r="R77" s="3"/>
-      <c r="S77" s="3"/>
-      <c r="T77" s="3"/>
-      <c r="U77" s="3"/>
-      <c r="V77" s="3"/>
-      <c r="W77" s="3"/>
-      <c r="X77" s="3"/>
+      <c r="K77" s="9">
+        <v>0</v>
+      </c>
+      <c r="L77" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M77" s="5"/>
+      <c r="N77" s="5"/>
+      <c r="O77" s="5"/>
+      <c r="P77" s="5"/>
+      <c r="Q77" s="5"/>
+      <c r="R77" s="5"/>
+      <c r="S77" s="5"/>
+      <c r="T77" s="5"/>
+      <c r="U77" s="5"/>
+      <c r="V77" s="5"/>
+      <c r="W77" s="5"/>
+      <c r="X77" s="5"/>
     </row>
-    <row r="78" spans="1:24">
-      <c r="A78" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B78" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C78" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D78" s="9" t="s">
+    <row r="78" spans="1:24" ht="39">
+      <c r="A78" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B78" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="D78" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="E78" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="F78" s="9">
-        <v>1</v>
-      </c>
-      <c r="G78" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="H78" s="11"/>
-      <c r="I78" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="J78" s="9" t="s">
+      <c r="E78" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F78" s="14">
+        <v>0</v>
+      </c>
+      <c r="G78" s="15" t="s">
+        <v>385</v>
+      </c>
+      <c r="H78" s="16"/>
+      <c r="I78" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="J78" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="K78" s="9">
-        <v>0</v>
-      </c>
-      <c r="L78" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M78" s="5"/>
-      <c r="N78" s="5"/>
-      <c r="O78" s="5"/>
-      <c r="P78" s="5"/>
-      <c r="Q78" s="5"/>
-      <c r="R78" s="5"/>
-      <c r="S78" s="5"/>
-      <c r="T78" s="5"/>
-      <c r="U78" s="5"/>
-      <c r="V78" s="5"/>
-      <c r="W78" s="5"/>
-      <c r="X78" s="5"/>
+      <c r="K78" s="14">
+        <v>0</v>
+      </c>
+      <c r="L78" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M78" s="3"/>
+      <c r="N78" s="3"/>
+      <c r="O78" s="3"/>
+      <c r="P78" s="3"/>
+      <c r="Q78" s="3"/>
+      <c r="R78" s="3"/>
+      <c r="S78" s="3"/>
+      <c r="T78" s="3"/>
+      <c r="U78" s="3"/>
+      <c r="V78" s="3"/>
+      <c r="W78" s="3"/>
+      <c r="X78" s="3"/>
     </row>
     <row r="79" spans="1:24" ht="26">
-      <c r="A79" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="B79" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="C79" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="D79" s="14" t="s">
+      <c r="A79" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D79" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E79" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F79" s="14">
-        <v>0</v>
-      </c>
-      <c r="G79" s="15" t="s">
-        <v>383</v>
-      </c>
-      <c r="H79" s="16"/>
-      <c r="I79" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="J79" s="14" t="s">
+      <c r="E79" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F79" s="9">
+        <v>0</v>
+      </c>
+      <c r="G79" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="H79" s="11"/>
+      <c r="I79" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="J79" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="K79" s="14">
-        <v>0</v>
-      </c>
-      <c r="L79" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M79" s="3"/>
-      <c r="N79" s="3"/>
-      <c r="O79" s="3"/>
-      <c r="P79" s="3"/>
-      <c r="Q79" s="3"/>
-      <c r="R79" s="3"/>
-      <c r="S79" s="3"/>
-      <c r="T79" s="3"/>
-      <c r="U79" s="3"/>
-      <c r="V79" s="3"/>
-      <c r="W79" s="3"/>
-      <c r="X79" s="3"/>
+      <c r="K79" s="9">
+        <v>0</v>
+      </c>
+      <c r="L79" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M79" s="5"/>
+      <c r="N79" s="5"/>
+      <c r="O79" s="5"/>
+      <c r="P79" s="5"/>
+      <c r="Q79" s="5"/>
+      <c r="R79" s="5"/>
+      <c r="S79" s="5"/>
+      <c r="T79" s="5"/>
+      <c r="U79" s="5"/>
+      <c r="V79" s="5"/>
+      <c r="W79" s="5"/>
+      <c r="X79" s="5"/>
     </row>
     <row r="80" spans="1:24" ht="26">
-      <c r="A80" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B80" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C80" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E80" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F80" s="9">
-        <v>0</v>
-      </c>
-      <c r="G80" s="10" t="s">
-        <v>384</v>
-      </c>
-      <c r="H80" s="11"/>
-      <c r="I80" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="J80" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="K80" s="9">
-        <v>0</v>
-      </c>
-      <c r="L80" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M80" s="5"/>
-      <c r="N80" s="5"/>
-      <c r="O80" s="5"/>
-      <c r="P80" s="5"/>
-      <c r="Q80" s="5"/>
-      <c r="R80" s="5"/>
-      <c r="S80" s="5"/>
-      <c r="T80" s="5"/>
-      <c r="U80" s="5"/>
-      <c r="V80" s="5"/>
-      <c r="W80" s="5"/>
-      <c r="X80" s="5"/>
+      <c r="A80" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B80" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C80" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D80" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E80" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F80" s="14">
+        <v>0</v>
+      </c>
+      <c r="G80" s="15" t="s">
+        <v>387</v>
+      </c>
+      <c r="H80" s="16" t="s">
+        <v>388</v>
+      </c>
+      <c r="I80" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="J80" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="K80" s="14">
+        <v>3</v>
+      </c>
+      <c r="L80" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M80" s="3"/>
+      <c r="N80" s="3"/>
+      <c r="O80" s="3"/>
+      <c r="P80" s="3"/>
+      <c r="Q80" s="3"/>
+      <c r="R80" s="3"/>
+      <c r="S80" s="3"/>
+      <c r="T80" s="3"/>
+      <c r="U80" s="3"/>
+      <c r="V80" s="3"/>
+      <c r="W80" s="3"/>
+      <c r="X80" s="3"/>
     </row>
     <row r="81" spans="1:24" ht="39">
-      <c r="A81" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="B81" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="C81" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="D81" s="14" t="s">
+      <c r="A81" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D81" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E81" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F81" s="14">
-        <v>0</v>
-      </c>
-      <c r="G81" s="15" t="s">
-        <v>385</v>
-      </c>
-      <c r="H81" s="16"/>
-      <c r="I81" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="J81" s="14" t="s">
+      <c r="E81" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F81" s="9">
+        <v>0</v>
+      </c>
+      <c r="G81" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="H81" s="11"/>
+      <c r="I81" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="J81" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="K81" s="14">
-        <v>0</v>
-      </c>
-      <c r="L81" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M81" s="3"/>
-      <c r="N81" s="3"/>
-      <c r="O81" s="3"/>
-      <c r="P81" s="3"/>
-      <c r="Q81" s="3"/>
-      <c r="R81" s="3"/>
-      <c r="S81" s="3"/>
-      <c r="T81" s="3"/>
-      <c r="U81" s="3"/>
-      <c r="V81" s="3"/>
-      <c r="W81" s="3"/>
-      <c r="X81" s="3"/>
+      <c r="K81" s="9">
+        <v>0</v>
+      </c>
+      <c r="L81" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M81" s="5"/>
+      <c r="N81" s="5"/>
+      <c r="O81" s="5"/>
+      <c r="P81" s="5"/>
+      <c r="Q81" s="5"/>
+      <c r="R81" s="5"/>
+      <c r="S81" s="5"/>
+      <c r="T81" s="5"/>
+      <c r="U81" s="5"/>
+      <c r="V81" s="5"/>
+      <c r="W81" s="5"/>
+      <c r="X81" s="5"/>
     </row>
     <row r="82" spans="1:24" ht="26">
-      <c r="A82" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B82" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C82" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E82" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F82" s="9">
-        <v>0</v>
-      </c>
-      <c r="G82" s="10" t="s">
-        <v>386</v>
-      </c>
-      <c r="H82" s="11"/>
-      <c r="I82" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="J82" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="K82" s="9">
-        <v>0</v>
-      </c>
-      <c r="L82" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M82" s="5"/>
-      <c r="N82" s="5"/>
-      <c r="O82" s="5"/>
-      <c r="P82" s="5"/>
-      <c r="Q82" s="5"/>
-      <c r="R82" s="5"/>
-      <c r="S82" s="5"/>
-      <c r="T82" s="5"/>
-      <c r="U82" s="5"/>
-      <c r="V82" s="5"/>
-      <c r="W82" s="5"/>
-      <c r="X82" s="5"/>
+      <c r="A82" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B82" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C82" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D82" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E82" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F82" s="14">
+        <v>1</v>
+      </c>
+      <c r="G82" s="15" t="s">
+        <v>390</v>
+      </c>
+      <c r="H82" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="I82" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="J82" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="K82" s="14">
+        <v>0</v>
+      </c>
+      <c r="L82" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
     </row>
     <row r="83" spans="1:24" ht="26">
-      <c r="A83" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="B83" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="C83" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="D83" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="E83" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F83" s="14">
-        <v>0</v>
-      </c>
-      <c r="G83" s="15" t="s">
-        <v>387</v>
-      </c>
-      <c r="H83" s="16" t="s">
-        <v>388</v>
-      </c>
-      <c r="I83" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="J83" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="K83" s="14">
-        <v>3</v>
-      </c>
-      <c r="L83" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3"/>
-      <c r="N83" s="3"/>
-      <c r="O83" s="3"/>
-      <c r="P83" s="3"/>
-      <c r="Q83" s="3"/>
-      <c r="R83" s="3"/>
-      <c r="S83" s="3"/>
-      <c r="T83" s="3"/>
-      <c r="U83" s="3"/>
-      <c r="V83" s="3"/>
-      <c r="W83" s="3"/>
-      <c r="X83" s="3"/>
+      <c r="A83" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C83" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E83" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F83" s="9">
+        <v>0</v>
+      </c>
+      <c r="G83" s="10" t="s">
+        <v>392</v>
+      </c>
+      <c r="H83" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="I83" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="J83" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="K83" s="9">
+        <v>4</v>
+      </c>
+      <c r="L83" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M83" s="5"/>
+      <c r="N83" s="5"/>
+      <c r="O83" s="5"/>
+      <c r="P83" s="5"/>
+      <c r="Q83" s="5"/>
+      <c r="R83" s="5"/>
+      <c r="S83" s="5"/>
+      <c r="T83" s="5"/>
+      <c r="U83" s="5"/>
+      <c r="V83" s="5"/>
+      <c r="W83" s="5"/>
+      <c r="X83" s="5"/>
     </row>
-    <row r="84" spans="1:24" ht="39">
-      <c r="A84" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B84" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C84" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D84" s="9" t="s">
+    <row r="84" spans="1:24" ht="26">
+      <c r="A84" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B84" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C84" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D84" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="E84" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F84" s="9">
-        <v>0</v>
-      </c>
-      <c r="G84" s="10" t="s">
-        <v>389</v>
-      </c>
-      <c r="H84" s="11"/>
-      <c r="I84" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="J84" s="9" t="s">
+      <c r="E84" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F84" s="14">
+        <v>0</v>
+      </c>
+      <c r="G84" s="15" t="s">
+        <v>394</v>
+      </c>
+      <c r="H84" s="16"/>
+      <c r="I84" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="J84" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="K84" s="9">
-        <v>0</v>
-      </c>
-      <c r="L84" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M84" s="5"/>
-      <c r="N84" s="5"/>
-      <c r="O84" s="5"/>
-      <c r="P84" s="5"/>
-      <c r="Q84" s="5"/>
-      <c r="R84" s="5"/>
-      <c r="S84" s="5"/>
-      <c r="T84" s="5"/>
-      <c r="U84" s="5"/>
-      <c r="V84" s="5"/>
-      <c r="W84" s="5"/>
-      <c r="X84" s="5"/>
+      <c r="K84" s="14">
+        <v>0</v>
+      </c>
+      <c r="L84" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M84" s="3"/>
+      <c r="N84" s="3"/>
+      <c r="O84" s="3"/>
+      <c r="P84" s="3"/>
+      <c r="Q84" s="3"/>
+      <c r="R84" s="3"/>
+      <c r="S84" s="3"/>
+      <c r="T84" s="3"/>
+      <c r="U84" s="3"/>
+      <c r="V84" s="3"/>
+      <c r="W84" s="3"/>
+      <c r="X84" s="3"/>
     </row>
     <row r="85" spans="1:24" ht="26">
-      <c r="A85" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="B85" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C85" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="D85" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="E85" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="F85" s="14">
-        <v>1</v>
-      </c>
-      <c r="G85" s="15" t="s">
-        <v>390</v>
-      </c>
-      <c r="H85" s="16" t="s">
-        <v>391</v>
-      </c>
-      <c r="I85" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="J85" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="K85" s="14">
-        <v>0</v>
-      </c>
-      <c r="L85" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M85" s="3"/>
-      <c r="N85" s="3"/>
-      <c r="O85" s="3"/>
-      <c r="P85" s="3"/>
-      <c r="Q85" s="3"/>
-      <c r="R85" s="3"/>
-      <c r="S85" s="3"/>
-      <c r="T85" s="3"/>
-      <c r="U85" s="3"/>
-      <c r="V85" s="3"/>
-      <c r="W85" s="3"/>
-      <c r="X85" s="3"/>
+      <c r="A85" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C85" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E85" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F85" s="9">
+        <v>0</v>
+      </c>
+      <c r="G85" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="H85" s="11"/>
+      <c r="I85" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="J85" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="K85" s="9">
+        <v>0</v>
+      </c>
+      <c r="L85" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M85" s="5"/>
+      <c r="N85" s="5"/>
+      <c r="O85" s="5"/>
+      <c r="P85" s="5"/>
+      <c r="Q85" s="5"/>
+      <c r="R85" s="5"/>
+      <c r="S85" s="5"/>
+      <c r="T85" s="5"/>
+      <c r="U85" s="5"/>
+      <c r="V85" s="5"/>
+      <c r="W85" s="5"/>
+      <c r="X85" s="5"/>
     </row>
-    <row r="86" spans="1:24" ht="26">
-      <c r="A86" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B86" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C86" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D86" s="9" t="s">
+    <row r="86" spans="1:24" ht="65">
+      <c r="A86" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B86" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C86" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D86" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E86" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F86" s="9">
-        <v>0</v>
-      </c>
-      <c r="G86" s="10" t="s">
-        <v>392</v>
-      </c>
-      <c r="H86" s="11" t="s">
-        <v>393</v>
-      </c>
-      <c r="I86" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="J86" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="K86" s="9">
-        <v>4</v>
-      </c>
-      <c r="L86" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M86" s="5"/>
-      <c r="N86" s="5"/>
-      <c r="O86" s="5"/>
-      <c r="P86" s="5"/>
-      <c r="Q86" s="5"/>
-      <c r="R86" s="5"/>
-      <c r="S86" s="5"/>
-      <c r="T86" s="5"/>
-      <c r="U86" s="5"/>
-      <c r="V86" s="5"/>
-      <c r="W86" s="5"/>
-      <c r="X86" s="5"/>
+      <c r="E86" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F86" s="14">
+        <v>0</v>
+      </c>
+      <c r="G86" s="15" t="s">
+        <v>396</v>
+      </c>
+      <c r="H86" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="I86" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J86" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="K86" s="14">
+        <v>3</v>
+      </c>
+      <c r="L86" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+      <c r="N86" s="3"/>
+      <c r="O86" s="3"/>
+      <c r="P86" s="3"/>
+      <c r="Q86" s="3"/>
+      <c r="R86" s="3"/>
+      <c r="S86" s="3"/>
+      <c r="T86" s="3"/>
+      <c r="U86" s="3"/>
+      <c r="V86" s="3"/>
+      <c r="W86" s="3"/>
+      <c r="X86" s="3"/>
     </row>
     <row r="87" spans="1:24" ht="26">
-      <c r="A87" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B87" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="C87" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="D87" s="14" t="s">
+      <c r="A87" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D87" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E87" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F87" s="14">
-        <v>0</v>
-      </c>
-      <c r="G87" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="H87" s="16"/>
-      <c r="I87" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="J87" s="14" t="s">
+      <c r="E87" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F87" s="9">
+        <v>0</v>
+      </c>
+      <c r="G87" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="H87" s="11"/>
+      <c r="I87" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="J87" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="K87" s="14">
-        <v>0</v>
-      </c>
-      <c r="L87" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M87" s="3"/>
-      <c r="N87" s="3"/>
-      <c r="O87" s="3"/>
-      <c r="P87" s="3"/>
-      <c r="Q87" s="3"/>
-      <c r="R87" s="3"/>
-      <c r="S87" s="3"/>
-      <c r="T87" s="3"/>
-      <c r="U87" s="3"/>
-      <c r="V87" s="3"/>
-      <c r="W87" s="3"/>
-      <c r="X87" s="3"/>
+      <c r="K87" s="9">
+        <v>0</v>
+      </c>
+      <c r="L87" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M87" s="5"/>
+      <c r="N87" s="5"/>
+      <c r="O87" s="5"/>
+      <c r="P87" s="5"/>
+      <c r="Q87" s="5"/>
+      <c r="R87" s="5"/>
+      <c r="S87" s="5"/>
+      <c r="T87" s="5"/>
+      <c r="U87" s="5"/>
+      <c r="V87" s="5"/>
+      <c r="W87" s="5"/>
+      <c r="X87" s="5"/>
     </row>
-    <row r="88" spans="1:24" ht="26">
-      <c r="A88" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="B88" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C88" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D88" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E88" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F88" s="9">
-        <v>0</v>
-      </c>
-      <c r="G88" s="10" t="s">
-        <v>395</v>
-      </c>
-      <c r="H88" s="11"/>
-      <c r="I88" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="J88" s="9" t="s">
+    <row r="88" spans="1:24" ht="52">
+      <c r="A88" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B88" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C88" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D88" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E88" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F88" s="14">
+        <v>0</v>
+      </c>
+      <c r="G88" s="15" t="s">
+        <v>399</v>
+      </c>
+      <c r="H88" s="16" t="s">
+        <v>400</v>
+      </c>
+      <c r="I88" s="17"/>
+      <c r="J88" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="K88" s="9">
-        <v>0</v>
-      </c>
-      <c r="L88" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M88" s="5"/>
-      <c r="N88" s="5"/>
-      <c r="O88" s="5"/>
-      <c r="P88" s="5"/>
-      <c r="Q88" s="5"/>
-      <c r="R88" s="5"/>
-      <c r="S88" s="5"/>
-      <c r="T88" s="5"/>
-      <c r="U88" s="5"/>
-      <c r="V88" s="5"/>
-      <c r="W88" s="5"/>
-      <c r="X88" s="5"/>
+      <c r="K88" s="14">
+        <v>0</v>
+      </c>
+      <c r="L88" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+      <c r="N88" s="3"/>
+      <c r="O88" s="3"/>
+      <c r="P88" s="3"/>
+      <c r="Q88" s="3"/>
+      <c r="R88" s="3"/>
+      <c r="S88" s="3"/>
+      <c r="T88" s="3"/>
+      <c r="U88" s="3"/>
+      <c r="V88" s="3"/>
+      <c r="W88" s="3"/>
+      <c r="X88" s="3"/>
     </row>
-    <row r="89" spans="1:24" ht="65">
-      <c r="A89" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B89" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C89" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D89" s="14" t="s">
+    <row r="89" spans="1:24" ht="26">
+      <c r="A89" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E89" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F89" s="9">
+        <v>0</v>
+      </c>
+      <c r="G89" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="H89" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="I89" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J89" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K89" s="9">
+        <v>3</v>
+      </c>
+      <c r="L89" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M89" s="5"/>
+      <c r="N89" s="5"/>
+      <c r="O89" s="5"/>
+      <c r="P89" s="5"/>
+      <c r="Q89" s="5"/>
+      <c r="R89" s="5"/>
+      <c r="S89" s="5"/>
+      <c r="T89" s="5"/>
+      <c r="U89" s="5"/>
+      <c r="V89" s="5"/>
+      <c r="W89" s="5"/>
+      <c r="X89" s="5"/>
+    </row>
+    <row r="90" spans="1:24">
+      <c r="A90" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B90" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C90" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D90" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E89" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F89" s="14">
-        <v>0</v>
-      </c>
-      <c r="G89" s="15" t="s">
-        <v>396</v>
-      </c>
-      <c r="H89" s="16" t="s">
-        <v>397</v>
-      </c>
-      <c r="I89" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="J89" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="K89" s="14">
+      <c r="E90" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F90" s="14">
+        <v>0</v>
+      </c>
+      <c r="G90" s="15" t="s">
+        <v>403</v>
+      </c>
+      <c r="H90" s="16" t="s">
+        <v>310</v>
+      </c>
+      <c r="I90" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="J90" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="K90" s="14">
         <v>3</v>
       </c>
-      <c r="L89" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3"/>
-      <c r="N89" s="3"/>
-      <c r="O89" s="3"/>
-      <c r="P89" s="3"/>
-      <c r="Q89" s="3"/>
-      <c r="R89" s="3"/>
-      <c r="S89" s="3"/>
-      <c r="T89" s="3"/>
-      <c r="U89" s="3"/>
-      <c r="V89" s="3"/>
-      <c r="W89" s="3"/>
-      <c r="X89" s="3"/>
-    </row>
-    <row r="90" spans="1:24" ht="26">
-      <c r="A90" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B90" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C90" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D90" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E90" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F90" s="9">
-        <v>0</v>
-      </c>
-      <c r="G90" s="10" t="s">
-        <v>398</v>
-      </c>
-      <c r="H90" s="11"/>
-      <c r="I90" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="J90" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="K90" s="9">
-        <v>0</v>
-      </c>
-      <c r="L90" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M90" s="5"/>
-      <c r="N90" s="5"/>
-      <c r="O90" s="5"/>
-      <c r="P90" s="5"/>
-      <c r="Q90" s="5"/>
-      <c r="R90" s="5"/>
-      <c r="S90" s="5"/>
-      <c r="T90" s="5"/>
-      <c r="U90" s="5"/>
-      <c r="V90" s="5"/>
-      <c r="W90" s="5"/>
-      <c r="X90" s="5"/>
+      <c r="L90" s="18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+      <c r="X90" s="3"/>
     </row>
     <row r="91" spans="1:24" ht="52">
-      <c r="A91" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B91" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C91" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="D91" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="E91" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F91" s="14">
-        <v>0</v>
-      </c>
-      <c r="G91" s="15" t="s">
-        <v>399</v>
-      </c>
-      <c r="H91" s="16" t="s">
-        <v>400</v>
-      </c>
-      <c r="I91" s="17"/>
-      <c r="J91" s="14" t="s">
+      <c r="A91" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B91" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C91" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D91" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E91" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F91" s="9">
+        <v>0</v>
+      </c>
+      <c r="G91" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="H91" s="11"/>
+      <c r="I91" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J91" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="K91" s="9">
+        <v>0</v>
+      </c>
+      <c r="L91" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M91" s="5"/>
+      <c r="N91" s="5"/>
+      <c r="O91" s="5"/>
+      <c r="P91" s="5"/>
+      <c r="Q91" s="5"/>
+      <c r="R91" s="5"/>
+      <c r="S91" s="5"/>
+      <c r="T91" s="5"/>
+      <c r="U91" s="5"/>
+      <c r="V91" s="5"/>
+      <c r="W91" s="5"/>
+      <c r="X91" s="5"/>
+    </row>
+    <row r="92" spans="1:24">
+      <c r="A92" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B92" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C92" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D92" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="E92" s="14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F92" s="14">
+        <v>0</v>
+      </c>
+      <c r="G92" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="H92" s="16"/>
+      <c r="I92" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="J92" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="K92" s="14">
+        <v>0</v>
+      </c>
+      <c r="L92" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="M92" s="3"/>
+      <c r="N92" s="3"/>
+      <c r="O92" s="3"/>
+      <c r="P92" s="3"/>
+      <c r="Q92" s="3"/>
+      <c r="R92" s="3"/>
+      <c r="S92" s="3"/>
+      <c r="T92" s="3"/>
+      <c r="U92" s="3"/>
+      <c r="V92" s="3"/>
+      <c r="W92" s="3"/>
+      <c r="X92" s="3"/>
+    </row>
+    <row r="93" spans="1:24" ht="39">
+      <c r="A93" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B93" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C93" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D93" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E93" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F93" s="9">
+        <v>1</v>
+      </c>
+      <c r="G93" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="H93" s="11"/>
+      <c r="I93" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="J93" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="K91" s="14">
-        <v>0</v>
-      </c>
-      <c r="L91" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3"/>
-      <c r="N91" s="3"/>
-      <c r="O91" s="3"/>
-      <c r="P91" s="3"/>
-      <c r="Q91" s="3"/>
-      <c r="R91" s="3"/>
-      <c r="S91" s="3"/>
-      <c r="T91" s="3"/>
-      <c r="U91" s="3"/>
-      <c r="V91" s="3"/>
-      <c r="W91" s="3"/>
-      <c r="X91" s="3"/>
+      <c r="K93" s="9">
+        <v>0</v>
+      </c>
+      <c r="L93" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="M93" s="5"/>
+      <c r="N93" s="5"/>
+      <c r="O93" s="5"/>
+      <c r="P93" s="5"/>
+      <c r="Q93" s="5"/>
+      <c r="R93" s="5"/>
+      <c r="S93" s="5"/>
+      <c r="T93" s="5"/>
+      <c r="U93" s="5"/>
+      <c r="V93" s="5"/>
+      <c r="W93" s="5"/>
+      <c r="X93" s="5"/>
     </row>
-    <row r="92" spans="1:24" ht="26">
-      <c r="A92" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B92" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C92" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D92" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E92" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F92" s="9">
-        <v>0</v>
-      </c>
-      <c r="G92" s="10" t="s">
-        <v>401</v>
-      </c>
-      <c r="H92" s="11" t="s">
-        <v>402</v>
-      </c>
-      <c r="I92" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="J92" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K92" s="9">
+    <row r="94" spans="1:24" ht="26.5" thickBot="1">
+      <c r="A94" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="B94" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C94" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="L92" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M92" s="5"/>
-      <c r="N92" s="5"/>
-      <c r="O92" s="5"/>
-      <c r="P92" s="5"/>
-      <c r="Q92" s="5"/>
-      <c r="R92" s="5"/>
-      <c r="S92" s="5"/>
-      <c r="T92" s="5"/>
-      <c r="U92" s="5"/>
-      <c r="V92" s="5"/>
-      <c r="W92" s="5"/>
-      <c r="X92" s="5"/>
+      <c r="D94" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="E94" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="F94" s="37">
+        <v>0</v>
+      </c>
+      <c r="G94" s="38" t="s">
+        <v>407</v>
+      </c>
+      <c r="H94" s="39"/>
+      <c r="I94" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="J94" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="K94" s="37">
+        <v>0</v>
+      </c>
+      <c r="L94" s="41" t="b">
+        <v>1</v>
+      </c>
+      <c r="M94" s="3"/>
+      <c r="N94" s="3"/>
+      <c r="O94" s="3"/>
+      <c r="P94" s="3"/>
+      <c r="Q94" s="3"/>
+      <c r="R94" s="3"/>
+      <c r="S94" s="3"/>
+      <c r="T94" s="3"/>
+      <c r="U94" s="3"/>
+      <c r="V94" s="3"/>
+      <c r="W94" s="3"/>
+      <c r="X94" s="3"/>
     </row>
-    <row r="93" spans="1:24">
-      <c r="A93" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B93" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C93" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="D93" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="E93" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F93" s="14">
-        <v>0</v>
-      </c>
-      <c r="G93" s="15" t="s">
-        <v>403</v>
-      </c>
-      <c r="H93" s="16" t="s">
-        <v>310</v>
-      </c>
-      <c r="I93" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="J93" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="K93" s="14">
-        <v>3</v>
-      </c>
-      <c r="L93" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="M93" s="3"/>
-      <c r="N93" s="3"/>
-      <c r="O93" s="3"/>
-      <c r="P93" s="3"/>
-      <c r="Q93" s="3"/>
-      <c r="R93" s="3"/>
-      <c r="S93" s="3"/>
-      <c r="T93" s="3"/>
-      <c r="U93" s="3"/>
-      <c r="V93" s="3"/>
-      <c r="W93" s="3"/>
-      <c r="X93" s="3"/>
+    <row r="95" spans="1:24" ht="15" thickTop="1">
+      <c r="A95" s="5"/>
+      <c r="B95" s="5"/>
+      <c r="C95" s="5"/>
+      <c r="D95" s="5"/>
+      <c r="E95" s="5"/>
+      <c r="F95" s="5"/>
+      <c r="G95" s="6"/>
+      <c r="H95" s="5"/>
+      <c r="I95" s="5"/>
+      <c r="J95" s="5"/>
+      <c r="K95" s="5"/>
+      <c r="L95" s="5"/>
+      <c r="M95" s="5"/>
+      <c r="N95" s="5"/>
+      <c r="O95" s="5"/>
+      <c r="P95" s="5"/>
+      <c r="Q95" s="5"/>
+      <c r="R95" s="5"/>
+      <c r="S95" s="5"/>
+      <c r="T95" s="5"/>
+      <c r="U95" s="5"/>
+      <c r="V95" s="5"/>
+      <c r="W95" s="5"/>
+      <c r="X95" s="5"/>
     </row>
-    <row r="94" spans="1:24" ht="52">
-      <c r="A94" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B94" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C94" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D94" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E94" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F94" s="9">
-        <v>0</v>
-      </c>
-      <c r="G94" s="10" t="s">
-        <v>404</v>
-      </c>
-      <c r="H94" s="11"/>
-      <c r="I94" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="J94" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="K94" s="9">
-        <v>0</v>
-      </c>
-      <c r="L94" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="M94" s="5"/>
-      <c r="N94" s="5"/>
-      <c r="O94" s="5"/>
-      <c r="P94" s="5"/>
-      <c r="Q94" s="5"/>
-      <c r="R94" s="5"/>
-      <c r="S94" s="5"/>
-      <c r="T94" s="5"/>
-      <c r="U94" s="5"/>
-      <c r="V94" s="5"/>
-      <c r="W94" s="5"/>
-      <c r="X94" s="5"/>
-    </row>
-    <row r="95" spans="1:24">
-      <c r="A95" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B95" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C95" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D95" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="E95" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F95" s="14">
-        <v>0</v>
-      </c>
-      <c r="G95" s="15" t="s">
-        <v>405</v>
-      </c>
-      <c r="H95" s="16"/>
-      <c r="I95" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="J95" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="K95" s="14">
-        <v>0</v>
-      </c>
-      <c r="L95" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M95" s="3"/>
-      <c r="N95" s="3"/>
-      <c r="O95" s="3"/>
-      <c r="P95" s="3"/>
-      <c r="Q95" s="3"/>
-      <c r="R95" s="3"/>
-      <c r="S95" s="3"/>
-      <c r="T95" s="3"/>
-      <c r="U95" s="3"/>
-      <c r="V95" s="3"/>
-      <c r="W95" s="3"/>
-      <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="1:24" ht="39">
-      <c r="A96" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B96" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C96" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D96" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E96" s="9" t="b">
-        <v>1</v>
-      </c>
-      <c r="F96" s="9">
-        <v>1</v>
-      </c>
-      <c r="G96" s="10" t="s">
-        <v>406</v>
-      </c>
-      <c r="H96" s="11"/>
-      <c r="I96" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="J96" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="K96" s="9">
-        <v>0</v>
-      </c>
-      <c r="L96" s="13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M96" s="5"/>
-      <c r="N96" s="5"/>
-      <c r="O96" s="5"/>
-      <c r="P96" s="5"/>
-      <c r="Q96" s="5"/>
-      <c r="R96" s="5"/>
-      <c r="S96" s="5"/>
-      <c r="T96" s="5"/>
-      <c r="U96" s="5"/>
-      <c r="V96" s="5"/>
-      <c r="W96" s="5"/>
-      <c r="X96" s="5"/>
-    </row>
-    <row r="97" spans="1:24" ht="26.5" thickBot="1">
-      <c r="A97" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="B97" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="C97" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="D97" s="37" t="s">
-        <v>2</v>
-      </c>
-      <c r="E97" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="F97" s="37">
-        <v>0</v>
-      </c>
-      <c r="G97" s="38" t="s">
-        <v>407</v>
-      </c>
-      <c r="H97" s="39"/>
-      <c r="I97" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="J97" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="K97" s="37">
-        <v>0</v>
-      </c>
-      <c r="L97" s="41" t="b">
-        <v>1</v>
-      </c>
-      <c r="M97" s="3"/>
-      <c r="N97" s="3"/>
-      <c r="O97" s="3"/>
-      <c r="P97" s="3"/>
-      <c r="Q97" s="3"/>
-      <c r="R97" s="3"/>
-      <c r="S97" s="3"/>
-      <c r="T97" s="3"/>
-      <c r="U97" s="3"/>
-      <c r="V97" s="3"/>
-      <c r="W97" s="3"/>
-      <c r="X97" s="3"/>
-    </row>
-    <row r="98" spans="1:24" ht="15" thickTop="1">
-      <c r="A98" s="5"/>
-      <c r="B98" s="5"/>
-      <c r="C98" s="5"/>
-      <c r="D98" s="5"/>
-      <c r="E98" s="5"/>
-      <c r="F98" s="5"/>
-      <c r="G98" s="6"/>
-      <c r="H98" s="5"/>
-      <c r="I98" s="5"/>
-      <c r="J98" s="5"/>
-      <c r="K98" s="5"/>
-      <c r="L98" s="5"/>
-      <c r="M98" s="5"/>
-      <c r="N98" s="5"/>
-      <c r="O98" s="5"/>
-      <c r="P98" s="5"/>
-      <c r="Q98" s="5"/>
-      <c r="R98" s="5"/>
-      <c r="S98" s="5"/>
-      <c r="T98" s="5"/>
-      <c r="U98" s="5"/>
-      <c r="V98" s="5"/>
-      <c r="W98" s="5"/>
-      <c r="X98" s="5"/>
-    </row>
-    <row r="99" spans="1:24">
-      <c r="A99" s="3"/>
-      <c r="B99" s="3"/>
-      <c r="C99" s="3"/>
-      <c r="D99" s="3"/>
-      <c r="E99" s="3"/>
-      <c r="F99" s="3"/>
-      <c r="G99" s="4"/>
-      <c r="H99" s="3"/>
-      <c r="I99" s="3"/>
-      <c r="J99" s="3"/>
-      <c r="K99" s="3"/>
-      <c r="L99" s="3"/>
-      <c r="M99" s="3"/>
-      <c r="N99" s="3"/>
-      <c r="O99" s="3"/>
-      <c r="P99" s="3"/>
-      <c r="Q99" s="3"/>
-      <c r="R99" s="3"/>
-      <c r="S99" s="3"/>
-      <c r="T99" s="3"/>
-      <c r="U99" s="3"/>
-      <c r="V99" s="3"/>
-      <c r="W99" s="3"/>
-      <c r="X99" s="3"/>
+    <row r="96" spans="1:24">
+      <c r="A96" s="3"/>
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="4"/>
+      <c r="H96" s="3"/>
+      <c r="I96" s="3"/>
+      <c r="J96" s="3"/>
+      <c r="K96" s="3"/>
+      <c r="L96" s="3"/>
+      <c r="M96" s="3"/>
+      <c r="N96" s="3"/>
+      <c r="O96" s="3"/>
+      <c r="P96" s="3"/>
+      <c r="Q96" s="3"/>
+      <c r="R96" s="3"/>
+      <c r="S96" s="3"/>
+      <c r="T96" s="3"/>
+      <c r="U96" s="3"/>
+      <c r="V96" s="3"/>
+      <c r="W96" s="3"/>
+      <c r="X96" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="K99:K153">
+  <conditionalFormatting sqref="K96:K150">
     <cfRule type="expression" dxfId="8" priority="1">
-      <formula>$K99=TRUE</formula>
+      <formula>$K96=TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10632,7 +10425,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD55B2B-46AB-414C-B861-32FE2FDC424F}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="17.26953125" customWidth="1"/>
@@ -10781,8 +10574,13 @@
         <v>445</v>
       </c>
     </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="70" t="s">
+        <v>472</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:F6">
+  <conditionalFormatting sqref="A2:F6 A8">
     <cfRule type="expression" dxfId="7" priority="17">
       <formula>$E2="Mark"</formula>
     </cfRule>
